--- a/TAZA/_документы/Бюджет ТАЗА – 2 месяца (ноябрь–декабрь).xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА – 2 месяца (ноябрь–декабрь).xlsx
@@ -1040,6 +1040,9 @@
     <t>Аренда_мес_2026</t>
   </si>
   <si>
+    <t>Месяцев аренды в 2026: заезд ориентировочно 21.10.2026 (III декада) — 11 дней октября + ноябрь + декабрь ≈ 2,35 мес.</t>
+  </si>
+  <si>
     <t>Мес_2026_новые</t>
   </si>
   <si>
@@ -1551,6 +1554,9 @@
   </si>
   <si>
     <t>Месяцев 2026 для новых сотрудников (зарплата, отчисления): приём с 01.11.2026, 2 мес. Действующие – 3 мес. Аренда – с 21.10.2026 (Аренда_мес_2026)</t>
+  </si>
+  <si>
+    <t>Мес. 2026 (новые – с 01.11)</t>
   </si>
   <si>
     <t>Декоративное растение напольное в высоком кашпо</t>
@@ -2109,12 +2115,6 @@
   </si>
   <si>
     <t>Разница с 250 млн (+ остаток / − не хватает)</t>
-  </si>
-  <si>
-    <t>Месяцев аренды в 2026: с 01.11.2026 – ноябрь и декабрь (2 мес.)</t>
-  </si>
-  <si>
-    <t>Мес. 2026 (все – с 01.11)</t>
   </si>
   <si>
     <t>Бюджет ЦАКФ на ноябрь–декабрь 2026 года, ₸</t>
@@ -2851,10 +2851,10 @@
         <v>0</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D3" s="35" t="s">
         <v>571</v>
@@ -2862,7 +2862,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B4" s="37">
         <f>SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$G$5:$G$36*(Штат!$I$5:$I$36&lt;=2))</f>
@@ -2879,7 +2879,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B5" s="37"/>
       <c r="C5" s="37"/>
@@ -2890,11 +2890,11 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B6" s="38">
-        <f>SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36*(Штат!$I$5:$I$36&lt;=2))</f>
-        <v>25551690</v>
+        <f>SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36*((Штат!$F$5:$F$36="действующий")+(Штат!$I$5:$I$36&lt;=2)))</f>
+        <v>32153930</v>
       </c>
       <c r="C6" s="38">
         <f>SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36*(Штат!$I$5:$I$36&lt;=3))</f>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="D6" s="40">
         <f>B6+C6</f>
-        <v>52586270</v>
+        <v>59188510</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B7" s="38">
         <v>0</v>
@@ -2923,7 +2923,7 @@
     </row>
     <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B8" s="38">
         <f>SUMPRODUCT(Аутсорс!$I$4:$I$10*((Аутсорс!$J$4:$J$10&lt;=1)+(Аутсорс!$J$4:$J$10&lt;=2)))</f>
@@ -2940,7 +2940,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B9" s="38">
         <f>Штат!$N$37</f>
@@ -2956,7 +2956,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="36" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B10" s="38">
         <f>Командировки!$G$12/2</f>
@@ -2973,7 +2973,7 @@
     </row>
     <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B11" s="38">
         <f>SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Оснащение")</f>
@@ -2990,11 +2990,11 @@
     </row>
     <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B12" s="38">
         <f>SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Офис")</f>
-        <v>10101943.199999999</v>
+        <v>11829706.848387096</v>
       </c>
       <c r="C12" s="38">
         <f>SUMIFS('Оснащение и офис'!$K$5:$K$77,'Оснащение и офис'!$A$5:$A$77,"Офис")</f>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="D12" s="40">
         <f>B12+C12</f>
-        <v>15314686.299999999</v>
+        <v>17042449.948387094</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="36" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B13" s="38">
         <f>SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Цифровые")</f>
@@ -3024,7 +3024,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="36" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B14" s="38">
         <f>SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Медиа")</f>
@@ -3041,11 +3041,11 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="39" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B15" s="40">
         <f>SUM(B6:B14)</f>
-        <v>58890259.20714286</v>
+        <v>67220262.855529949</v>
       </c>
       <c r="C15" s="40">
         <f>SUM(C6:C14)</f>
@@ -3053,16 +3053,16 @@
       </c>
       <c r="D15" s="40">
         <f>B15+C15</f>
-        <v>112432313.55714285</v>
+        <v>120762317.20552996</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B16" s="38">
         <f>B15*Резерв+SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Прочие")</f>
-        <v>6239025.9207142862</v>
+        <v>7072026.2855529953</v>
       </c>
       <c r="C16" s="38">
         <f>C15*Резерв+SUMIFS('Оснащение и офис'!$K$5:$K$77,'Оснащение и офис'!$A$5:$A$77,"Прочие")</f>
@@ -3070,16 +3070,16 @@
       </c>
       <c r="D16" s="40">
         <f>B16+C16</f>
-        <v>11593231.355714288</v>
+        <v>12426231.720552996</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="36" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B17" s="38">
         <f>((B11+B12+B13+B14)-'Оснащение и офис'!$J$59)*(1+Резерв)*НДС</f>
-        <v>3357582.2720000003</v>
+        <v>3661668.6741161295</v>
       </c>
       <c r="C17" s="38">
         <f>((C11+C12+C13+C14)-'Оснащение и офис'!$K$59)*(1+Резерв)*НДС</f>
@@ -3087,16 +3087,16 @@
       </c>
       <c r="D17" s="40">
         <f>B17+C17</f>
-        <v>4824868.2416000003</v>
+        <v>5128954.6437161295</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B18" s="42">
         <f>B15+B16+B17</f>
-        <v>68486867.399857149</v>
+        <v>77953957.815199077</v>
       </c>
       <c r="C18" s="42">
         <f>C15+C16+C17</f>
@@ -3104,12 +3104,12 @@
       </c>
       <c r="D18" s="42">
         <f>B18+C18</f>
-        <v>128850413.15445715</v>
+        <v>138317503.56979907</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="39" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B19" s="40">
         <f>Проекты!$H$13</f>
@@ -3126,11 +3126,11 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="43" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B20" s="44">
         <f>B18+B19</f>
-        <v>106732840.73319048</v>
+        <v>116199931.14853242</v>
       </c>
       <c r="C20" s="44">
         <f>C18+C19</f>
@@ -3138,26 +3138,26 @@
       </c>
       <c r="D20" s="44">
         <f>B20+C20</f>
-        <v>198927559.82112381</v>
+        <v>208394650.23646575</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="106" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B22" s="44">
         <f>B20</f>
-        <v>106732840.73319048</v>
+        <v>116199931.14853242</v>
       </c>
       <c r="C22" s="44">
         <f>B22+C20</f>
-        <v>198927559.82112381</v>
+        <v>208394650.23646575</v>
       </c>
       <c r="D22" s="44"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="106" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B23" s="44"/>
       <c r="C23" s="44"/>
@@ -3167,19 +3167,19 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="43" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B24" s="44">
         <f>$D$23-B22</f>
-        <v>143267159.26680952</v>
+        <v>133800068.85146758</v>
       </c>
       <c r="C24" s="44">
         <f>$D$23-C22</f>
-        <v>51072440.178876191</v>
+        <v>41605349.763534248</v>
       </c>
       <c r="D24" s="44">
         <f>D23-D20</f>
-        <v>51072440.178876191</v>
+        <v>41605349.763534248</v>
       </c>
     </row>
   </sheetData>
@@ -3206,7 +3206,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="107" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B1" s="107"/>
       <c r="C1" s="107"/>
@@ -3225,25 +3225,25 @@
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F3" s="50" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3255,13 +3255,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -3276,13 +3276,13 @@
     </row>
     <row r="6" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -3298,13 +3298,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B7" s="57" t="s">
+        <v>422</v>
+      </c>
+      <c r="C7" s="55" t="s">
         <v>420</v>
-      </c>
-      <c r="C7" s="55" t="s">
-        <v>418</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -3319,13 +3319,13 @@
     </row>
     <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D8" s="55">
         <v>1</v>
@@ -3340,13 +3340,13 @@
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D9" s="74">
         <v>100</v>
@@ -3361,13 +3361,13 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D10" s="74">
         <v>100</v>
@@ -3383,10 +3383,10 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51"/>
       <c r="B11" s="57" t="s">
+        <v>428</v>
+      </c>
+      <c r="C11" s="55" t="s">
         <v>426</v>
-      </c>
-      <c r="C11" s="55" t="s">
-        <v>424</v>
       </c>
       <c r="D11" s="74">
         <v>1</v>
@@ -3401,13 +3401,13 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D12" s="55">
         <v>4</v>
@@ -3422,13 +3422,13 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="51" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B13" s="75" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C13" s="76" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D13" s="76">
         <v>1</v>
@@ -3444,7 +3444,7 @@
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="51"/>
       <c r="B14" s="59" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C14" s="49"/>
       <c r="D14" s="55"/>
@@ -3457,7 +3457,7 @@
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="51"/>
       <c r="B15" s="60" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C15" s="61"/>
       <c r="D15" s="61"/>
@@ -3514,7 +3514,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="107" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B1" s="107"/>
       <c r="C1" s="107"/>
@@ -3533,25 +3533,25 @@
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F3" s="50" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3563,13 +3563,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D5" s="55">
         <v>4</v>
@@ -3584,13 +3584,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -3606,13 +3606,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -3628,7 +3628,7 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51"/>
       <c r="B8" s="59" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C8" s="49"/>
       <c r="D8" s="55"/>
@@ -3641,7 +3641,7 @@
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="51"/>
       <c r="B9" s="60" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C9" s="61"/>
       <c r="D9" s="61"/>
@@ -3698,7 +3698,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="107" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B1" s="107"/>
       <c r="C1" s="107"/>
@@ -3717,25 +3717,25 @@
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F3" s="50" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3747,13 +3747,13 @@
     </row>
     <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D5" s="55">
         <v>6</v>
@@ -3768,13 +3768,13 @@
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -3790,13 +3790,13 @@
     </row>
     <row r="7" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -3811,13 +3811,13 @@
     </row>
     <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D8" s="55">
         <v>9</v>
@@ -3832,13 +3832,13 @@
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D9" s="74">
         <v>32</v>
@@ -3853,13 +3853,13 @@
     </row>
     <row r="10" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D10" s="55">
         <v>3</v>
@@ -3874,13 +3874,13 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D11" s="55">
         <v>3</v>
@@ -3897,7 +3897,7 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51"/>
       <c r="B12" s="59" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C12" s="49"/>
       <c r="D12" s="55"/>
@@ -3910,7 +3910,7 @@
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="51"/>
       <c r="B13" s="60" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C13" s="61"/>
       <c r="D13" s="61"/>
@@ -3964,7 +3964,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="107" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B1" s="107"/>
       <c r="C1" s="107"/>
@@ -3983,25 +3983,25 @@
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F3" s="50" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -4013,13 +4013,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -4034,13 +4034,13 @@
     </row>
     <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -4057,7 +4057,7 @@
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51"/>
       <c r="B7" s="59" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C7" s="49"/>
       <c r="D7" s="55"/>
@@ -4070,7 +4070,7 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51"/>
       <c r="B8" s="60" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C8" s="61"/>
       <c r="D8" s="61"/>
@@ -4127,7 +4127,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="107" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B1" s="107"/>
       <c r="C1" s="107"/>
@@ -4146,25 +4146,25 @@
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F3" s="50" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -4176,13 +4176,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -4198,7 +4198,7 @@
     <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="51"/>
       <c r="B6" s="59" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C6" s="49"/>
       <c r="D6" s="55"/>
@@ -4212,7 +4212,7 @@
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51"/>
       <c r="B7" s="60" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C7" s="61"/>
       <c r="D7" s="61"/>
@@ -4270,7 +4270,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -4317,7 +4317,7 @@
         <v>10500</v>
       </c>
       <c r="G5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -4453,7 +4453,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -4604,7 +4604,7 @@
         <v>188</v>
       </c>
       <c r="B20" s="104" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C20" s="104" t="s">
         <v>103</v>
@@ -4621,13 +4621,13 @@
         <v>4548</v>
       </c>
       <c r="G20" s="104" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="32"/>
@@ -4893,7 +4893,7 @@
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -5184,14 +5184,14 @@
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B15" s="8">
         <f>ROUND(0.29%*12*SUMIFS(Штат!$H$5:$H$36,Штат!$E$5:$E$36,"штат",Штат!$F$5:$F$36,"новая"),-3)</f>
         <v>713000</v>
       </c>
       <c r="C15" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5382,7 +5382,7 @@
         <v>4869152.0999999996</v>
       </c>
       <c r="C32" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5393,7 +5393,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5420,17 +5420,17 @@
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="41" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -5442,7 +5442,7 @@
         <v>340.67</v>
       </c>
       <c r="C42" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -5453,7 +5453,7 @@
         <v>13500</v>
       </c>
       <c r="C43" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -5465,7 +5465,7 @@
         <v>230107.1</v>
       </c>
       <c r="C44" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -5476,7 +5476,7 @@
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -5487,7 +5487,7 @@
         <v>40000</v>
       </c>
       <c r="C46" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -5519,10 +5519,11 @@
         <v>218</v>
       </c>
       <c r="B49" s="15">
-        <v>2</v>
+        <f>11/31+2</f>
+        <v>2.3548387096774195</v>
       </c>
       <c r="C49" t="s">
-        <v>568</v>
+        <v>219</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -5543,13 +5544,13 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B52" s="15">
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -5578,7 +5579,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5610,7 +5611,7 @@
         <v>72</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>73</v>
@@ -5619,22 +5620,22 @@
         <v>74</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>569</v>
+        <v>391</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>76</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>77</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q4" s="88" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -5642,10 +5643,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>78</v>
@@ -5663,7 +5664,7 @@
         <v>1600000</v>
       </c>
       <c r="I5" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="18">
         <f t="shared" ref="J5:J27" si="0">IF(E5="штат",ROUND(Ставка_СН*H5*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H5+Ставка_СО*MIN(H5*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H5,Кап_ООСМС*МЗП),0),ROUND(H5*НДС,0))</f>
@@ -5675,11 +5676,11 @@
       </c>
       <c r="L5" s="19">
         <f t="shared" ref="L5:L36" si="2">IF(AND(F5="новая",I5=1),Мес_2026_новые,MAX(0,4-I5))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5" s="18">
         <f t="shared" ref="M5:M36" si="3">K5*L5</f>
-        <v>3636460</v>
+        <v>5454690</v>
       </c>
       <c r="N5" s="18">
         <f t="shared" ref="N5:N36" si="4">IF(AND(E5="штат",F5="новая"),ОСНС_полис*G5/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
@@ -5687,10 +5688,10 @@
       </c>
       <c r="O5" s="18">
         <f t="shared" ref="O5:O36" si="5">M5+N5</f>
-        <v>3636460</v>
+        <v>5454690</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="Q5" s="89"/>
     </row>
@@ -5699,10 +5700,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>81</v>
@@ -5720,7 +5721,7 @@
         <v>1400000</v>
       </c>
       <c r="I6" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" s="18">
         <f t="shared" si="0"/>
@@ -5732,11 +5733,11 @@
       </c>
       <c r="L6" s="19">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6" s="18">
         <f t="shared" si="3"/>
-        <v>3189340</v>
+        <v>4784010</v>
       </c>
       <c r="N6" s="18">
         <f t="shared" si="4"/>
@@ -5744,10 +5745,10 @@
       </c>
       <c r="O6" s="18">
         <f t="shared" si="5"/>
-        <v>3189340</v>
+        <v>4784010</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Q6" s="89"/>
     </row>
@@ -5756,10 +5757,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>81</v>
@@ -5777,7 +5778,7 @@
         <v>1400000</v>
       </c>
       <c r="I7" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7" s="18">
         <f t="shared" si="0"/>
@@ -5789,11 +5790,11 @@
       </c>
       <c r="L7" s="19">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M7" s="18">
         <f t="shared" si="3"/>
-        <v>3189340</v>
+        <v>4784010</v>
       </c>
       <c r="N7" s="18">
         <f t="shared" si="4"/>
@@ -5801,10 +5802,10 @@
       </c>
       <c r="O7" s="18">
         <f t="shared" si="5"/>
-        <v>3189340</v>
+        <v>4784010</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q7" s="89"/>
     </row>
@@ -5816,7 +5817,7 @@
         <v>207</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>81</v>
@@ -5861,7 +5862,7 @@
         <v>3223292.3809523811</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q8" s="89">
         <v>1</v>
@@ -5872,13 +5873,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>79</v>
@@ -5920,7 +5921,7 @@
         <v>1516842.3809523811</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q9" s="89"/>
     </row>
@@ -5929,13 +5930,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>79</v>
@@ -5977,7 +5978,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q10" s="89">
         <v>1</v>
@@ -5988,16 +5989,16 @@
         <v>6</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F11" s="20" t="s">
         <v>82</v>
@@ -6036,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="21" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q11" s="89"/>
     </row>
@@ -6045,13 +6046,13 @@
         <v>6</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>79</v>
@@ -6093,7 +6094,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q12" s="89"/>
     </row>
@@ -6102,13 +6103,13 @@
         <v>14</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>79</v>
@@ -6150,7 +6151,7 @@
         <v>2552612.3809523811</v>
       </c>
       <c r="P13" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q13" s="89"/>
     </row>
@@ -6159,13 +6160,13 @@
         <v>15</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>79</v>
@@ -6207,7 +6208,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q14" s="89">
         <v>1</v>
@@ -6218,13 +6219,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E15" s="16" t="s">
         <v>79</v>
@@ -6266,7 +6267,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P15" s="17" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q15" s="89">
         <v>1</v>
@@ -6277,13 +6278,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C16" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="D16" s="17" t="s">
         <v>242</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>241</v>
       </c>
       <c r="E16" s="16" t="s">
         <v>79</v>
@@ -6325,7 +6326,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P16" s="17" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q16" s="89">
         <v>1</v>
@@ -6336,13 +6337,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E17" s="16" t="s">
         <v>79</v>
@@ -6384,7 +6385,7 @@
         <v>0</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="Q17" s="89"/>
     </row>
@@ -6393,13 +6394,13 @@
         <v>19</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C18" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="D18" s="17" t="s">
         <v>242</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>241</v>
       </c>
       <c r="E18" s="16" t="s">
         <v>79</v>
@@ -6441,7 +6442,7 @@
         <v>0</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="Q18" s="89"/>
     </row>
@@ -6450,13 +6451,13 @@
         <v>19</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C19" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="D19" s="17" t="s">
         <v>242</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>241</v>
       </c>
       <c r="E19" s="16" t="s">
         <v>79</v>
@@ -6498,7 +6499,7 @@
         <v>1658372.3809523811</v>
       </c>
       <c r="P19" s="17" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q19" s="89"/>
     </row>
@@ -6507,13 +6508,13 @@
         <v>23</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E20" s="16" t="s">
         <v>79</v>
@@ -6555,7 +6556,7 @@
         <v>2999732.3809523811</v>
       </c>
       <c r="P20" s="17" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q20" s="89">
         <v>1</v>
@@ -6566,16 +6567,16 @@
         <v>24</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>82</v>
@@ -6614,7 +6615,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="21" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q21" s="89"/>
     </row>
@@ -6623,13 +6624,13 @@
         <v>25</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>79</v>
@@ -6671,7 +6672,7 @@
         <v>2999732.3809523811</v>
       </c>
       <c r="P22" s="17" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q22" s="89"/>
     </row>
@@ -6680,10 +6681,10 @@
         <v>26</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D23" s="17" t="s">
         <v>208</v>
@@ -6728,7 +6729,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q23" s="89">
         <v>1</v>
@@ -6739,16 +6740,16 @@
         <v>27</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D24" s="21" t="s">
         <v>208</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F24" s="20" t="s">
         <v>82</v>
@@ -6787,7 +6788,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="21" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q24" s="89"/>
     </row>
@@ -6796,16 +6797,16 @@
         <v>28</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D25" s="21" t="s">
         <v>208</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F25" s="20" t="s">
         <v>82</v>
@@ -6844,7 +6845,7 @@
         <v>0</v>
       </c>
       <c r="P25" s="21" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q25" s="89"/>
     </row>
@@ -6853,10 +6854,10 @@
         <v>29</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>208</v>
@@ -6901,7 +6902,7 @@
         <v>1658372.3809523811</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q26" s="89">
         <v>1</v>
@@ -6912,10 +6913,10 @@
         <v>30</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D27" s="17" t="s">
         <v>208</v>
@@ -6960,7 +6961,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q27" s="89"/>
     </row>
@@ -6969,10 +6970,10 @@
         <v>31</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D28" s="17" t="s">
         <v>208</v>
@@ -7017,7 +7018,7 @@
         <v>1658372.3809523811</v>
       </c>
       <c r="P28" s="17" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q28" s="89"/>
     </row>
@@ -7026,16 +7027,16 @@
         <v>32</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D29" s="21" t="s">
         <v>208</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F29" s="20" t="s">
         <v>82</v>
@@ -7074,7 +7075,7 @@
         <v>0</v>
       </c>
       <c r="P29" s="21" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q29" s="89"/>
     </row>
@@ -7083,7 +7084,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C30" s="17" t="s">
         <v>83</v>
@@ -7104,7 +7105,7 @@
         <v>1400000</v>
       </c>
       <c r="I30" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J30" s="18">
         <f t="shared" si="25"/>
@@ -7116,11 +7117,11 @@
       </c>
       <c r="L30" s="19">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M30" s="18">
         <f t="shared" si="3"/>
-        <v>3189340</v>
+        <v>4784010</v>
       </c>
       <c r="N30" s="18">
         <f t="shared" si="4"/>
@@ -7128,10 +7129,10 @@
       </c>
       <c r="O30" s="18">
         <f t="shared" si="5"/>
-        <v>3189340</v>
+        <v>4784010</v>
       </c>
       <c r="P30" s="17" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q30" s="89"/>
     </row>
@@ -7140,7 +7141,7 @@
         <v>34</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>84</v>
@@ -7197,13 +7198,13 @@
         <v>35</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E32" s="16" t="s">
         <v>79</v>
@@ -7245,7 +7246,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q32" s="89"/>
     </row>
@@ -7254,13 +7255,13 @@
         <v>35</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E33" s="16" t="s">
         <v>79</v>
@@ -7302,7 +7303,7 @@
         <v>1881932.3809523811</v>
       </c>
       <c r="P33" s="17" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Q33" s="89"/>
     </row>
@@ -7311,13 +7312,13 @@
         <v>35</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E34" s="16" t="s">
         <v>79</v>
@@ -7359,7 +7360,7 @@
         <v>1881932.3809523811</v>
       </c>
       <c r="P34" s="17" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="Q34" s="89"/>
     </row>
@@ -7368,16 +7369,16 @@
         <v>36</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D35" s="21" t="s">
         <v>206</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F35" s="20" t="s">
         <v>82</v>
@@ -7416,7 +7417,7 @@
         <v>0</v>
       </c>
       <c r="P35" s="21" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q35" s="89"/>
     </row>
@@ -7425,16 +7426,16 @@
         <v>37</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D36" s="21" t="s">
         <v>206</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F36" s="20" t="s">
         <v>82</v>
@@ -7473,7 +7474,7 @@
         <v>0</v>
       </c>
       <c r="P36" s="21" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q36" s="89"/>
     </row>
@@ -7481,7 +7482,7 @@
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
@@ -7503,7 +7504,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="6">
         <f>SUM(M5:M36)</f>
-        <v>52586270</v>
+        <v>59188510</v>
       </c>
       <c r="N37" s="6">
         <f t="shared" ref="N37:O37" si="37">SUM(N5:N36)</f>
@@ -7511,13 +7512,13 @@
       </c>
       <c r="O37" s="6">
         <f t="shared" si="37"/>
-        <v>53197412.857142851</v>
+        <v>59799652.857142851</v>
       </c>
       <c r="P37" s="7"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G38">
         <f>SUM(G8:G12)+SUM(G13:G29)</f>
@@ -7530,7 +7531,7 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G39">
         <f>G37-G38</f>
@@ -7543,12 +7544,12 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C41" s="7" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="H42" s="5">
         <f>SUMPRODUCT(Q5:Q36,H5:H36)</f>
@@ -7557,7 +7558,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="H43" s="5">
         <f>H42*(Ставка_ОПВР+Ставка_ООСМС+Ставка_СН*(1-Ставка_ОПВ-Ставка_ВОСМС))</f>
@@ -7566,7 +7567,7 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C44" s="7" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="H44" s="6">
         <f>H42+H43</f>
@@ -7575,7 +7576,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -7606,7 +7607,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -7620,25 +7621,25 @@
         <v>68</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F3" s="103" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G3" s="103" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H3" s="25" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J3" s="25" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K3" s="25" t="s">
         <v>75</v>
@@ -7652,13 +7653,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>206</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E4" s="28">
         <v>867500</v>
@@ -7696,13 +7697,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>206</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E5" s="28">
         <v>425600</v>
@@ -7740,13 +7741,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E6" s="28">
         <v>1000000</v>
@@ -7784,13 +7785,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E7" s="28">
         <v>1000000</v>
@@ -7828,13 +7829,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E8" s="28">
         <v>700000</v>
@@ -7872,13 +7873,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E9" s="28">
         <v>700000</v>
@@ -7916,13 +7917,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E10" s="28">
         <v>700000</v>
@@ -7958,7 +7959,7 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="30"/>
       <c r="B11" s="30" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
@@ -7991,7 +7992,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12" s="24" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>
@@ -8013,12 +8014,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -8029,48 +8030,48 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B4" s="93">
         <v>0.1</v>
       </c>
       <c r="C4" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B5" s="94">
         <f>Ставка_ОПВР+Ставка_ООСМС+Ставка_СН*(1-Ставка_ОПВ-Ставка_ВОСМС)</f>
         <v>0.1178</v>
       </c>
       <c r="C5" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="95" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B7" s="95" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C7" s="95" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D7" s="95" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E7" s="95" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="F7" s="95" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="G7" s="95" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -8191,48 +8192,48 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="98" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B14" s="97">
         <f>$B$4*(1+$B$5)</f>
         <v>0.11177999999999999</v>
       </c>
       <c r="C14" s="98" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="98" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B15" s="97">
         <f>$B$4*(1+$B$5)*(1+НДС)</f>
         <v>0.12966479999999997</v>
       </c>
       <c r="C15" s="98" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="99" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B18" s="99"/>
       <c r="C18" s="99"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="98" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B19" s="96">
         <f>Аутсорс!E11</f>
@@ -8242,7 +8243,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="98" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B20" s="96">
         <f>Аутсорс!F11</f>
@@ -8252,7 +8253,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="100" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B21" s="101">
         <f>Аутсорс!F11*2</f>
@@ -8262,7 +8263,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="100" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B22" s="101">
         <f>B21*(1+НДС)</f>
@@ -8272,7 +8273,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="98" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B23" s="96">
         <f>Аутсорс!L11</f>
@@ -8282,7 +8283,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
   </sheetData>
@@ -8306,7 +8307,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8331,7 +8332,7 @@
         <v>89</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>90</v>
@@ -8411,7 +8412,7 @@
     </row>
     <row r="8" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C8">
         <f>SUMIFS(Штат!$G$5:$G$36,Штат!$B$5:$B$36,"Департамент социологических*",Штат!$E$5:$E$36,"штат")</f>
@@ -8434,7 +8435,7 @@
     </row>
     <row r="9" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C9">
         <f>SUMIFS(Штат!$G$5:$G$36,Штат!$B$5:$B$36,"Департамент проектного управления*",Штат!$E$5:$E$36,"штат")</f>
@@ -8457,7 +8458,7 @@
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C10">
         <f>SUM(Штат!G20:G21)</f>
@@ -8480,7 +8481,7 @@
     </row>
     <row r="11" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C11">
         <f>SUM(Штат!G22:G29)</f>
@@ -8541,12 +8542,12 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8569,7 +8570,7 @@
         <v>95</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>96</v>
@@ -8578,13 +8579,13 @@
         <v>90</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8610,7 +8611,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I57" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
@@ -8651,7 +8652,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
@@ -8692,7 +8693,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="0"/>
@@ -8715,7 +8716,7 @@
         <v>97</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C8" t="s">
         <v>99</v>
@@ -8734,7 +8735,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="0"/>
@@ -8757,7 +8758,7 @@
         <v>97</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C9" s="80" t="s">
         <v>99</v>
@@ -8776,7 +8777,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" ref="I9" si="1">IF(F9="разово",IF(G9&lt;=3,D9*E9,0),IF(F9="мес",D9*E9*MAX(0,4-G9),D9*E9*MAX(0,4-G9)/12))</f>
@@ -8799,7 +8800,7 @@
         <v>97</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C10" s="81" t="s">
         <v>99</v>
@@ -8818,7 +8819,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" ref="I10" si="2">IF(F10="разово",IF(G10&lt;=3,D10*E10,0),IF(F10="мес",D10*E10*MAX(0,4-G10),D10*E10*MAX(0,4-G10)/12))</f>
@@ -8841,7 +8842,7 @@
         <v>97</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C11" s="82" t="s">
         <v>99</v>
@@ -8860,7 +8861,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" ref="I11" si="3">IF(F11="разово",IF(G11&lt;=3,D11*E11,0),IF(F11="мес",D11*E11*MAX(0,4-G11),D11*E11*MAX(0,4-G11)/12))</f>
@@ -8883,7 +8884,7 @@
         <v>97</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C12" t="s">
         <v>99</v>
@@ -8902,7 +8903,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="0"/>
@@ -8925,7 +8926,7 @@
         <v>97</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C13" s="84" t="s">
         <v>99</v>
@@ -8944,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="I13" s="5">
         <f>IF(F13="разово",IF(G13&lt;=3,D13*E13,0),IF(F13="мес",D13*E13*MAX(0,4-G13),D13*E13*MAX(0,4-G13)/12))</f>
@@ -8967,7 +8968,7 @@
         <v>97</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C14" s="84" t="s">
         <v>99</v>
@@ -8986,7 +8987,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="I14" s="5">
         <f>IF(F14="разово",IF(G14&lt;=3,D14*E14,0),IF(F14="мес",D14*E14*MAX(0,4-G14),D14*E14*MAX(0,4-G14)/12))</f>
@@ -9009,7 +9010,7 @@
         <v>97</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C15" s="83" t="s">
         <v>99</v>
@@ -9028,7 +9029,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" ref="I15" si="4">IF(F15="разово",IF(G15&lt;=3,D15*E15,0),IF(F15="мес",D15*E15*MAX(0,4-G15),D15*E15*MAX(0,4-G15)/12))</f>
@@ -9051,7 +9052,7 @@
         <v>97</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C16" s="92" t="s">
         <v>99</v>
@@ -9070,7 +9071,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" ref="I16:I21" si="5">IF(F16="разово",IF(G16&lt;=3,D16*E16,0),IF(F16="мес",D16*E16*MAX(0,4-G16),D16*E16*MAX(0,4-G16)/12))</f>
@@ -9093,7 +9094,7 @@
         <v>97</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C17" s="87" t="s">
         <v>103</v>
@@ -9112,7 +9113,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="5"/>
@@ -9135,7 +9136,7 @@
         <v>97</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C18" s="91" t="s">
         <v>103</v>
@@ -9154,7 +9155,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="5"/>
@@ -9177,7 +9178,7 @@
         <v>97</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C19" s="85" t="s">
         <v>99</v>
@@ -9196,7 +9197,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="5"/>
@@ -9219,7 +9220,7 @@
         <v>97</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C20" s="86" t="s">
         <v>103</v>
@@ -9238,7 +9239,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="5"/>
@@ -9261,7 +9262,7 @@
         <v>97</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C21" s="86" t="s">
         <v>103</v>
@@ -9280,7 +9281,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="5"/>
@@ -9342,7 +9343,7 @@
         <v>97</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C23" t="s">
         <v>103</v>
@@ -9381,7 +9382,7 @@
         <v>97</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C24" t="s">
         <v>103</v>
@@ -9399,7 +9400,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
@@ -9440,7 +9441,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
@@ -9505,7 +9506,7 @@
         <v>97</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C27" s="86" t="s">
         <v>103</v>
@@ -9524,7 +9525,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="I27" s="5">
         <f>IF(F27="разово",IF(G27&lt;=3,D27*E27,0),IF(F27="мес",D27*E27*MAX(0,4-G27),D27*E27*MAX(0,4-G27)/12))</f>
@@ -9645,7 +9646,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
@@ -9750,7 +9751,7 @@
         <v>97</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C33" t="s">
         <v>99</v>
@@ -9767,7 +9768,7 @@
         <v>1</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="0"/>
@@ -9790,10 +9791,10 @@
         <v>97</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C34" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="10">
@@ -9807,7 +9808,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
@@ -9830,7 +9831,7 @@
         <v>97</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C35" t="s">
         <v>99</v>
@@ -9847,7 +9848,7 @@
         <v>1</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I35" s="5">
         <f t="shared" si="0"/>
@@ -9870,7 +9871,7 @@
         <v>97</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C36" t="s">
         <v>103</v>
@@ -9887,7 +9888,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" si="0"/>
@@ -9910,7 +9911,7 @@
         <v>97</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C37" t="s">
         <v>99</v>
@@ -9929,7 +9930,7 @@
         <v>1</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="0"/>
@@ -9952,7 +9953,7 @@
         <v>97</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C38" t="s">
         <v>99</v>
@@ -9971,7 +9972,7 @@
         <v>1</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="0"/>
@@ -9994,7 +9995,7 @@
         <v>97</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C39" t="s">
         <v>99</v>
@@ -10013,7 +10014,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="0"/>
@@ -10036,7 +10037,7 @@
         <v>97</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C40" t="s">
         <v>99</v>
@@ -10055,7 +10056,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I40" s="5">
         <f t="shared" si="0"/>
@@ -10078,7 +10079,7 @@
         <v>97</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C41" t="s">
         <v>99</v>
@@ -10097,7 +10098,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I41" s="5">
         <f t="shared" ref="I41" si="6">IF(F41="разово",IF(G41&lt;=3,D41*E41,0),IF(F41="мес",D41*E41*MAX(0,4-G41),D41*E41*MAX(0,4-G41)/12))</f>
@@ -10120,7 +10121,7 @@
         <v>97</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C42" s="105" t="s">
         <v>99</v>
@@ -10139,7 +10140,7 @@
         <v>1</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="I42" s="5">
         <f>IF(F42="разово",IF(G42&lt;=3,D42*E42,0),IF(F42="мес",D42*E42*MAX(0,4-G42),D42*E42*MAX(0,4-G42)/12))</f>
@@ -10162,7 +10163,7 @@
         <v>97</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C43" t="s">
         <v>99</v>
@@ -10181,7 +10182,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I43" s="5">
         <f t="shared" si="0"/>
@@ -10204,7 +10205,7 @@
         <v>97</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C44" t="s">
         <v>99</v>
@@ -10223,7 +10224,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="I44" s="5">
         <f t="shared" si="0"/>
@@ -10246,7 +10247,7 @@
         <v>97</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C45" s="90" t="s">
         <v>99</v>
@@ -10265,7 +10266,7 @@
         <v>1</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="I45" s="5">
         <f>IF(F45="разово",IF(G45&lt;=3,D45*E45,0),IF(F45="мес",D45*E45*MAX(0,4-G45),D45*E45*MAX(0,4-G45)/12))</f>
@@ -10288,7 +10289,7 @@
         <v>97</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C46" t="s">
         <v>103</v>
@@ -10306,7 +10307,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="0"/>
@@ -10409,7 +10410,7 @@
         <v>97</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C49" t="s">
         <v>108</v>
@@ -10428,7 +10429,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I49" s="5">
         <f t="shared" si="0"/>
@@ -10451,7 +10452,7 @@
         <v>97</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C50" t="s">
         <v>103</v>
@@ -10490,7 +10491,7 @@
         <v>97</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C51" t="s">
         <v>99</v>
@@ -10509,7 +10510,7 @@
         <v>1</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I51" s="5">
         <f t="shared" ref="I51" si="7">IF(F51="разово",IF(G51&lt;=3,D51*E51,0),IF(F51="мес",D51*E51*MAX(0,4-G51),D51*E51*MAX(0,4-G51)/12))</f>
@@ -10532,7 +10533,7 @@
         <v>97</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C52" t="s">
         <v>99</v>
@@ -10551,7 +10552,7 @@
         <v>1</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="I52" s="5">
         <f t="shared" ref="I52:I54" si="8">IF(F52="разово",IF(G52&lt;=3,D52*E52,0),IF(F52="мес",D52*E52*MAX(0,4-G52),D52*E52*MAX(0,4-G52)/12))</f>
@@ -10574,7 +10575,7 @@
         <v>97</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C53" t="s">
         <v>103</v>
@@ -10593,7 +10594,7 @@
         <v>1</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="I53" s="5">
         <f t="shared" si="8"/>
@@ -10616,7 +10617,7 @@
         <v>97</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C54" t="s">
         <v>99</v>
@@ -10635,7 +10636,7 @@
         <v>1</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="I54" s="5">
         <f t="shared" si="8"/>
@@ -10736,7 +10737,7 @@
         <v>97</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C57" t="s">
         <v>99</v>
@@ -10794,15 +10795,15 @@
         <v>1</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I58" s="5">
         <f>D58*E58*Аренда_мес_2026</f>
-        <v>9738304.1999999993</v>
+        <v>11466067.848387096</v>
       </c>
       <c r="J58" s="5">
         <f>$D58*$E58*(Аренда_мес_2026-1)</f>
-        <v>4869152.0999999996</v>
+        <v>6596915.7483870964</v>
       </c>
       <c r="K58" s="5">
         <f>IF($F58="разово",IF($L58=12,$I58,0),IF($F58="мес",$D58*$E58*($G58&lt;=3),IF($F58="год",$D58*$E58/12*($G58&lt;=3),$I58/2)))</f>
@@ -10834,7 +10835,7 @@
         <v>1</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I59" s="5">
         <f t="shared" ref="I59:I77" si="9">IF(F59="разово",IF(G59&lt;=3,D59*E59,0),IF(F59="мес",D59*E59*MAX(0,4-G59),D59*E59*MAX(0,4-G59)/12))</f>
@@ -10875,7 +10876,7 @@
         <v>2</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="I60" s="5">
         <f t="shared" si="9"/>
@@ -10970,10 +10971,10 @@
         <v>111</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C63" s="105" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D63" s="9">
         <v>2</v>
@@ -10989,7 +10990,7 @@
         <v>2</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="I63" s="5">
         <f>IF(F63="разово",IF(G63&lt;=3,D63*E63,0),IF(F63="мес",D63*E63*MAX(0,4-G63),D63*E63*MAX(0,4-G63)/12))</f>
@@ -11047,7 +11048,7 @@
         <v>111</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C65" t="s">
         <v>113</v>
@@ -11066,7 +11067,7 @@
         <v>2</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I65" s="5">
         <f t="shared" si="9"/>
@@ -11087,7 +11088,7 @@
         <v>111</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C66" t="s">
         <v>103</v>
@@ -11106,7 +11107,7 @@
         <v>1</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I66" s="5">
         <f t="shared" ref="I66" si="10">IF(F66="разово",IF(G66&lt;=3,D66*E66,0),IF(F66="мес",D66*E66*MAX(0,4-G66),D66*E66*MAX(0,4-G66)/12))</f>
@@ -11184,7 +11185,7 @@
         <v>2</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I68" s="5">
         <f t="shared" si="9"/>
@@ -11281,7 +11282,7 @@
         <v>121</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C71" t="s">
         <v>126</v>
@@ -11300,7 +11301,7 @@
         <v>2</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="I71" s="5">
         <f t="shared" si="9"/>
@@ -11323,10 +11324,10 @@
         <v>121</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C72" s="102" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D72" s="9">
         <v>1</v>
@@ -11341,7 +11342,7 @@
         <v>2</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="I72" s="5">
         <f>IF(F72="разово",IF(G72&lt;=3,D72*E72,0),IF(F72="мес",D72*E72*MAX(0,4-G72),D72*E72*MAX(0,4-G72)/12))</f>
@@ -11362,15 +11363,15 @@
         <v>128</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C73" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D73" s="9"/>
       <c r="E73" s="10"/>
       <c r="F73" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G73" s="9"/>
       <c r="H73" s="4"/>
@@ -11466,7 +11467,7 @@
         <v>132</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C76" t="s">
         <v>103</v>
@@ -11484,7 +11485,7 @@
         <v>1</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="I76" s="5">
         <f t="shared" si="9"/>
@@ -11507,7 +11508,7 @@
         <v>132</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C77" t="s">
         <v>130</v>
@@ -11563,7 +11564,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -11592,26 +11593,26 @@
         <v>90</v>
       </c>
       <c r="H4" s="34" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="I4" s="34" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10"/>
       <c r="F5" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G5" s="5">
         <f>'Taza talqy'!F12</f>
@@ -11628,18 +11629,18 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10"/>
       <c r="F6" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G6" s="5">
         <f>'Презентация офисе'!F15</f>
@@ -11656,18 +11657,18 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C7" t="s">
         <v>234</v>
-      </c>
-      <c r="C7" t="s">
-        <v>233</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="10"/>
       <c r="F7" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G7" s="5">
         <f>'креативные проекты'!F9</f>
@@ -11684,18 +11685,18 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="10"/>
       <c r="F8" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G8" s="5">
         <f>'Информ сопровождение'!F13</f>
@@ -11712,18 +11713,18 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="10"/>
       <c r="F9" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G9" s="5">
         <f>'Соц исследования'!F8</f>
@@ -11740,18 +11741,18 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="10"/>
       <c r="F10" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G10" s="5">
         <f>'Разработка платформы'!F7</f>
@@ -11782,7 +11783,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -11825,7 +11826,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="107" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B1" s="107"/>
       <c r="C1" s="107"/>
@@ -11844,25 +11845,25 @@
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F3" s="50" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -11874,13 +11875,13 @@
     </row>
     <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B5" s="54" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D5" s="55">
         <v>56</v>
@@ -11895,13 +11896,13 @@
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D6" s="55">
         <v>56</v>
@@ -11917,13 +11918,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B7" s="57" t="s">
+        <v>409</v>
+      </c>
+      <c r="C7" s="55" t="s">
         <v>407</v>
-      </c>
-      <c r="C7" s="55" t="s">
-        <v>405</v>
       </c>
       <c r="D7" s="55">
         <v>6</v>
@@ -11938,13 +11939,13 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D8" s="55">
         <v>6</v>
@@ -11959,13 +11960,13 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D9" s="55">
         <v>6</v>
@@ -11980,13 +11981,13 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D10" s="55">
         <v>48</v>
@@ -12002,7 +12003,7 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51"/>
       <c r="B11" s="59" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C11" s="49"/>
       <c r="D11" s="55"/>
@@ -12015,7 +12016,7 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51"/>
       <c r="B12" s="60" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C12" s="61"/>
       <c r="D12" s="61"/>

--- a/TAZA/_документы/Бюджет ТАЗА – 2 месяца (ноябрь–декабрь).xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА – 2 месяца (ноябрь–декабрь).xlsx
@@ -381,7 +381,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="573">
   <si>
     <t>Статья</t>
   </si>
@@ -1401,9 +1401,6 @@
   </si>
   <si>
     <t>Б. Первоочередные проекты (лист «Проекты»)</t>
-  </si>
-  <si>
-    <t>ВСЕГО (А + Б)</t>
   </si>
   <si>
     <t>2. Аккумуляторы</t>
@@ -2121,6 +2118,12 @@
   </si>
   <si>
     <t>Итого ноябрь–декабрь 2026</t>
+  </si>
+  <si>
+    <t>В. Долг по зарплате и налогам за июль–октябрь 2026 (4 действующих работника Фонда: оклады и отчисления работодателя за 4 месяца, выплата в ноябре)</t>
+  </si>
+  <si>
+    <t>ВСЕГО (А + Б + В)</t>
   </si>
 </sst>
 </file>
@@ -2558,13 +2561,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2832,7 +2835,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="80.7109375" style="4" customWidth="1"/>
@@ -2843,7 +2846,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -2851,13 +2854,13 @@
         <v>0</v>
       </c>
       <c r="B3" s="35" t="s">
+        <v>562</v>
+      </c>
+      <c r="C3" s="35" t="s">
         <v>563</v>
       </c>
-      <c r="C3" s="35" t="s">
-        <v>564</v>
-      </c>
       <c r="D3" s="35" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2872,7 +2875,7 @@
         <f>SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$G$5:$G$36*(Штат!$I$5:$I$36&lt;=3))</f>
         <v>22</v>
       </c>
-      <c r="D4" s="109">
+      <c r="D4" s="107">
         <f>C4</f>
         <v>22</v>
       </c>
@@ -2883,7 +2886,7 @@
       </c>
       <c r="B5" s="37"/>
       <c r="C5" s="37"/>
-      <c r="D5" s="109">
+      <c r="D5" s="107">
         <f>Штат!G38</f>
         <v>15</v>
       </c>
@@ -2893,21 +2896,21 @@
         <v>332</v>
       </c>
       <c r="B6" s="38">
-        <f>SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36*((Штат!$F$5:$F$36="действующий")+(Штат!$I$5:$I$36&lt;=2)))</f>
-        <v>32153930</v>
+        <f>SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36*(Штат!$I$5:$I$36&lt;=2))</f>
+        <v>25551690</v>
       </c>
       <c r="C6" s="38">
         <f>SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36*(Штат!$I$5:$I$36&lt;=3))</f>
         <v>27034580</v>
       </c>
       <c r="D6" s="40">
-        <f>B6+C6</f>
-        <v>59188510</v>
+        <f t="shared" ref="D6:D21" si="0">B6+C6</f>
+        <v>52586270</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B7" s="38">
         <v>0</v>
@@ -2917,13 +2920,13 @@
         <v>9389520</v>
       </c>
       <c r="D7" s="40">
-        <f>B7+C7</f>
+        <f t="shared" si="0"/>
         <v>9389520</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B8" s="38">
         <f>SUMPRODUCT(Аутсорс!$I$4:$I$10*((Аутсорс!$J$4:$J$10&lt;=1)+(Аутсорс!$J$4:$J$10&lt;=2)))</f>
@@ -2934,13 +2937,13 @@
         <v>6881596</v>
       </c>
       <c r="D8" s="40">
-        <f>B8+C8</f>
+        <f t="shared" si="0"/>
         <v>13763192</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B9" s="38">
         <f>Штат!$N$37</f>
@@ -2950,7 +2953,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="40">
-        <f>B9+C9</f>
+        <f t="shared" si="0"/>
         <v>611142.85714285716</v>
       </c>
     </row>
@@ -2967,7 +2970,7 @@
         <v>1899506.25</v>
       </c>
       <c r="D10" s="40">
-        <f>B10+C10</f>
+        <f t="shared" si="0"/>
         <v>3799012.5</v>
       </c>
     </row>
@@ -2984,13 +2987,13 @@
         <v>1695609</v>
       </c>
       <c r="D11" s="40">
-        <f>B11+C11</f>
+        <f t="shared" si="0"/>
         <v>14032042.9</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B12" s="38">
         <f>SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Офис")</f>
@@ -3001,7 +3004,7 @@
         <v>5212743.0999999996</v>
       </c>
       <c r="D12" s="40">
-        <f>B12+C12</f>
+        <f t="shared" si="0"/>
         <v>17042449.948387094</v>
       </c>
     </row>
@@ -3018,7 +3021,7 @@
         <v>253500</v>
       </c>
       <c r="D13" s="40">
-        <f>B13+C13</f>
+        <f t="shared" si="0"/>
         <v>586447</v>
       </c>
     </row>
@@ -3035,7 +3038,7 @@
         <v>1175000</v>
       </c>
       <c r="D14" s="40">
-        <f>B14+C14</f>
+        <f t="shared" si="0"/>
         <v>2350000</v>
       </c>
     </row>
@@ -3045,37 +3048,37 @@
       </c>
       <c r="B15" s="40">
         <f>SUM(B6:B14)</f>
-        <v>67220262.855529949</v>
+        <v>60618022.855529949</v>
       </c>
       <c r="C15" s="40">
         <f>SUM(C6:C14)</f>
         <v>53542054.350000001</v>
       </c>
       <c r="D15" s="40">
-        <f>B15+C15</f>
-        <v>120762317.20552996</v>
+        <f t="shared" si="0"/>
+        <v>114160077.20552996</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B16" s="38">
         <f>B15*Резерв+SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Прочие")</f>
-        <v>7072026.2855529953</v>
+        <v>6411802.2855529953</v>
       </c>
       <c r="C16" s="38">
         <f>C15*Резерв+SUMIFS('Оснащение и офис'!$K$5:$K$77,'Оснащение и офис'!$A$5:$A$77,"Прочие")</f>
         <v>5354205.4350000005</v>
       </c>
       <c r="D16" s="40">
-        <f>B16+C16</f>
-        <v>12426231.720552996</v>
+        <f t="shared" si="0"/>
+        <v>11766007.720552996</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="36" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B17" s="38">
         <f>((B11+B12+B13+B14)-'Оснащение и офис'!$J$59)*(1+Резерв)*НДС</f>
@@ -3086,7 +3089,7 @@
         <v>1467285.9696000002</v>
       </c>
       <c r="D17" s="40">
-        <f>B17+C17</f>
+        <f t="shared" si="0"/>
         <v>5128954.6437161295</v>
       </c>
     </row>
@@ -3096,15 +3099,15 @@
       </c>
       <c r="B18" s="42">
         <f>B15+B16+B17</f>
-        <v>77953957.815199077</v>
+        <v>70691493.815199077</v>
       </c>
       <c r="C18" s="42">
         <f>C15+C16+C17</f>
         <v>60363545.754600003</v>
       </c>
       <c r="D18" s="42">
-        <f>B18+C18</f>
-        <v>138317503.56979907</v>
+        <f t="shared" si="0"/>
+        <v>131055039.56979908</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -3120,66 +3123,82 @@
         <v>31831173.333333332</v>
       </c>
       <c r="D19" s="40">
-        <f>B19+C19</f>
+        <f t="shared" si="0"/>
         <v>70077146.666666672</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="43" t="s">
-        <v>340</v>
-      </c>
-      <c r="B20" s="44">
-        <f>B18+B19</f>
-        <v>116199931.14853242</v>
-      </c>
-      <c r="C20" s="44">
-        <f>C18+C19</f>
+    <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="39" t="s">
+        <v>571</v>
+      </c>
+      <c r="B20" s="40">
+        <f>4*SUMPRODUCT((Штат!$F$5:$F$36="действующий")*(Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36)</f>
+        <v>26408960</v>
+      </c>
+      <c r="C20" s="40">
+        <v>0</v>
+      </c>
+      <c r="D20" s="40">
+        <f>SUM(B20:C20)</f>
+        <v>26408960</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="43" t="s">
+        <v>572</v>
+      </c>
+      <c r="B21" s="44">
+        <f>B18+B19+B20</f>
+        <v>135346427.14853242</v>
+      </c>
+      <c r="C21" s="44">
+        <f>C18+C19+C20</f>
         <v>92194719.087933332</v>
       </c>
-      <c r="D20" s="44">
-        <f>B20+C20</f>
-        <v>208394650.23646575</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="106" t="s">
-        <v>567</v>
-      </c>
-      <c r="B22" s="44">
-        <f>B20</f>
-        <v>116199931.14853242</v>
-      </c>
-      <c r="C22" s="44">
-        <f>B22+C20</f>
-        <v>208394650.23646575</v>
-      </c>
-      <c r="D22" s="44"/>
+      <c r="D21" s="44">
+        <f>D18+D19+D20</f>
+        <v>227541146.23646575</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="106" t="s">
+        <v>566</v>
+      </c>
+      <c r="B23" s="44">
+        <f>B21</f>
+        <v>135346427.14853242</v>
+      </c>
+      <c r="C23" s="44">
+        <f>B23+C21</f>
+        <v>227541146.23646575</v>
+      </c>
+      <c r="D23" s="44"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="106" t="s">
+        <v>567</v>
+      </c>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44">
+        <v>250000000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="43" t="s">
         <v>568</v>
       </c>
-      <c r="B23" s="44"/>
-      <c r="C23" s="44"/>
-      <c r="D23" s="44">
-        <v>250000000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="43" t="s">
-        <v>569</v>
-      </c>
-      <c r="B24" s="44">
-        <f>$D$23-B22</f>
-        <v>133800068.85146758</v>
-      </c>
-      <c r="C24" s="44">
-        <f>$D$23-C22</f>
-        <v>41605349.763534248</v>
-      </c>
-      <c r="D24" s="44">
-        <f>D23-D20</f>
-        <v>41605349.763534248</v>
+      <c r="B25" s="44">
+        <f>$D$24-B23</f>
+        <v>114653572.85146758</v>
+      </c>
+      <c r="C25" s="44">
+        <f>$D$24-C23</f>
+        <v>22458853.763534248</v>
+      </c>
+      <c r="D25" s="44">
+        <f>D24-D21</f>
+        <v>22458853.763534248</v>
       </c>
     </row>
   </sheetData>
@@ -3205,45 +3224,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="107" t="s">
-        <v>418</v>
-      </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
+      <c r="A1" s="108" t="s">
+        <v>417</v>
+      </c>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>395</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>396</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>397</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>398</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>399</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3255,13 +3274,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B5" s="57" t="s">
+        <v>418</v>
+      </c>
+      <c r="C5" s="55" t="s">
         <v>419</v>
-      </c>
-      <c r="C5" s="55" t="s">
-        <v>420</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -3276,13 +3295,13 @@
     </row>
     <row r="6" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -3298,13 +3317,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -3319,13 +3338,13 @@
     </row>
     <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B8" s="57" t="s">
+        <v>422</v>
+      </c>
+      <c r="C8" s="55" t="s">
         <v>423</v>
-      </c>
-      <c r="C8" s="55" t="s">
-        <v>424</v>
       </c>
       <c r="D8" s="55">
         <v>1</v>
@@ -3340,13 +3359,13 @@
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B9" s="57" t="s">
+        <v>424</v>
+      </c>
+      <c r="C9" s="55" t="s">
         <v>425</v>
-      </c>
-      <c r="C9" s="55" t="s">
-        <v>426</v>
       </c>
       <c r="D9" s="74">
         <v>100</v>
@@ -3361,13 +3380,13 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D10" s="74">
         <v>100</v>
@@ -3383,10 +3402,10 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51"/>
       <c r="B11" s="57" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D11" s="74">
         <v>1</v>
@@ -3401,13 +3420,13 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D12" s="55">
         <v>4</v>
@@ -3422,13 +3441,13 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="51" t="s">
+        <v>428</v>
+      </c>
+      <c r="B13" s="75" t="s">
         <v>429</v>
       </c>
-      <c r="B13" s="75" t="s">
-        <v>430</v>
-      </c>
       <c r="C13" s="76" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D13" s="76">
         <v>1</v>
@@ -3444,7 +3463,7 @@
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="51"/>
       <c r="B14" s="59" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C14" s="49"/>
       <c r="D14" s="55"/>
@@ -3457,7 +3476,7 @@
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="51"/>
       <c r="B15" s="60" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C15" s="61"/>
       <c r="D15" s="61"/>
@@ -3513,45 +3532,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="107" t="s">
-        <v>431</v>
-      </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
+      <c r="A1" s="108" t="s">
+        <v>430</v>
+      </c>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>395</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>396</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>397</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>398</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>399</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3563,13 +3582,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B5" s="57" t="s">
+        <v>431</v>
+      </c>
+      <c r="C5" s="55" t="s">
         <v>432</v>
-      </c>
-      <c r="C5" s="55" t="s">
-        <v>433</v>
       </c>
       <c r="D5" s="55">
         <v>4</v>
@@ -3584,13 +3603,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B6" s="57" t="s">
+        <v>433</v>
+      </c>
+      <c r="C6" s="55" t="s">
         <v>434</v>
-      </c>
-      <c r="C6" s="55" t="s">
-        <v>435</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -3606,13 +3625,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -3628,7 +3647,7 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51"/>
       <c r="B8" s="59" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C8" s="49"/>
       <c r="D8" s="55"/>
@@ -3641,7 +3660,7 @@
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="51"/>
       <c r="B9" s="60" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C9" s="61"/>
       <c r="D9" s="61"/>
@@ -3697,45 +3716,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="107" t="s">
-        <v>437</v>
-      </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
+      <c r="A1" s="108" t="s">
+        <v>436</v>
+      </c>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>395</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>396</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>397</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>398</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>399</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3747,13 +3766,13 @@
     </row>
     <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D5" s="55">
         <v>6</v>
@@ -3768,13 +3787,13 @@
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -3790,13 +3809,13 @@
     </row>
     <row r="7" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -3811,13 +3830,13 @@
     </row>
     <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D8" s="55">
         <v>9</v>
@@ -3832,13 +3851,13 @@
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D9" s="74">
         <v>32</v>
@@ -3853,13 +3872,13 @@
     </row>
     <row r="10" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D10" s="55">
         <v>3</v>
@@ -3874,13 +3893,13 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D11" s="55">
         <v>3</v>
@@ -3897,7 +3916,7 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51"/>
       <c r="B12" s="59" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C12" s="49"/>
       <c r="D12" s="55"/>
@@ -3910,7 +3929,7 @@
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="51"/>
       <c r="B13" s="60" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C13" s="61"/>
       <c r="D13" s="61"/>
@@ -3963,45 +3982,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="107" t="s">
-        <v>445</v>
-      </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
+      <c r="A1" s="108" t="s">
+        <v>444</v>
+      </c>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>395</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>396</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>397</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>398</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>399</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -4013,13 +4032,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -4034,13 +4053,13 @@
     </row>
     <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -4057,7 +4076,7 @@
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51"/>
       <c r="B7" s="59" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C7" s="49"/>
       <c r="D7" s="55"/>
@@ -4070,7 +4089,7 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51"/>
       <c r="B8" s="60" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C8" s="61"/>
       <c r="D8" s="61"/>
@@ -4126,45 +4145,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="107" t="s">
-        <v>448</v>
-      </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
+      <c r="A1" s="108" t="s">
+        <v>447</v>
+      </c>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>395</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>396</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>397</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>398</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>399</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -4176,13 +4195,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -4198,7 +4217,7 @@
     <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="51"/>
       <c r="B6" s="59" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C6" s="49"/>
       <c r="D6" s="55"/>
@@ -4212,7 +4231,7 @@
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51"/>
       <c r="B7" s="60" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C7" s="61"/>
       <c r="D7" s="61"/>
@@ -4270,7 +4289,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -4453,7 +4472,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -4604,7 +4623,7 @@
         <v>188</v>
       </c>
       <c r="B20" s="104" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C20" s="104" t="s">
         <v>103</v>
@@ -4621,13 +4640,13 @@
         <v>4548</v>
       </c>
       <c r="G20" s="104" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="32"/>
@@ -4893,7 +4912,7 @@
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -5184,14 +5203,14 @@
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B15" s="8">
         <f>ROUND(0.29%*12*SUMIFS(Штат!$H$5:$H$36,Штат!$E$5:$E$36,"штат",Штат!$F$5:$F$36,"новая"),-3)</f>
         <v>713000</v>
       </c>
       <c r="C15" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5476,7 +5495,7 @@
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -5550,7 +5569,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -5620,13 +5639,13 @@
         <v>74</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>76</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>77</v>
@@ -5635,7 +5654,7 @@
         <v>316</v>
       </c>
       <c r="Q4" s="88" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -5664,7 +5683,7 @@
         <v>1600000</v>
       </c>
       <c r="I5" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="18">
         <f t="shared" ref="J5:J27" si="0">IF(E5="штат",ROUND(Ставка_СН*H5*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H5+Ставка_СО*MIN(H5*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H5,Кап_ООСМС*МЗП),0),ROUND(H5*НДС,0))</f>
@@ -5676,11 +5695,11 @@
       </c>
       <c r="L5" s="19">
         <f t="shared" ref="L5:L36" si="2">IF(AND(F5="новая",I5=1),Мес_2026_новые,MAX(0,4-I5))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M5" s="18">
         <f t="shared" ref="M5:M36" si="3">K5*L5</f>
-        <v>5454690</v>
+        <v>3636460</v>
       </c>
       <c r="N5" s="18">
         <f t="shared" ref="N5:N36" si="4">IF(AND(E5="штат",F5="новая"),ОСНС_полис*G5/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
@@ -5688,10 +5707,10 @@
       </c>
       <c r="O5" s="18">
         <f t="shared" ref="O5:O36" si="5">M5+N5</f>
-        <v>5454690</v>
+        <v>3636460</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="Q5" s="89"/>
     </row>
@@ -5703,7 +5722,7 @@
         <v>263</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>81</v>
@@ -5721,7 +5740,7 @@
         <v>1400000</v>
       </c>
       <c r="I6" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" s="18">
         <f t="shared" si="0"/>
@@ -5733,11 +5752,11 @@
       </c>
       <c r="L6" s="19">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M6" s="18">
         <f t="shared" si="3"/>
-        <v>4784010</v>
+        <v>3189340</v>
       </c>
       <c r="N6" s="18">
         <f t="shared" si="4"/>
@@ -5745,10 +5764,10 @@
       </c>
       <c r="O6" s="18">
         <f t="shared" si="5"/>
-        <v>4784010</v>
+        <v>3189340</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="Q6" s="89"/>
     </row>
@@ -5778,7 +5797,7 @@
         <v>1400000</v>
       </c>
       <c r="I7" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" s="18">
         <f t="shared" si="0"/>
@@ -5790,11 +5809,11 @@
       </c>
       <c r="L7" s="19">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M7" s="18">
         <f t="shared" si="3"/>
-        <v>4784010</v>
+        <v>3189340</v>
       </c>
       <c r="N7" s="18">
         <f t="shared" si="4"/>
@@ -5802,10 +5821,10 @@
       </c>
       <c r="O7" s="18">
         <f t="shared" si="5"/>
-        <v>4784010</v>
+        <v>3189340</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Q7" s="89"/>
     </row>
@@ -5817,7 +5836,7 @@
         <v>207</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>81</v>
@@ -5862,7 +5881,7 @@
         <v>3223292.3809523811</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Q8" s="89">
         <v>1</v>
@@ -5879,7 +5898,7 @@
         <v>237</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>79</v>
@@ -5921,7 +5940,7 @@
         <v>1516842.3809523811</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q9" s="89"/>
     </row>
@@ -5933,7 +5952,7 @@
         <v>236</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D10" s="17" t="s">
         <v>239</v>
@@ -5978,7 +5997,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Q10" s="89">
         <v>1</v>
@@ -5992,7 +6011,7 @@
         <v>236</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D11" s="21" t="s">
         <v>239</v>
@@ -6037,7 +6056,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="21" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q11" s="89"/>
     </row>
@@ -6208,7 +6227,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q14" s="89">
         <v>1</v>
@@ -6267,7 +6286,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P15" s="17" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Q15" s="89">
         <v>1</v>
@@ -6326,7 +6345,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P16" s="17" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q16" s="89">
         <v>1</v>
@@ -6385,7 +6404,7 @@
         <v>0</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="Q17" s="89"/>
     </row>
@@ -6442,7 +6461,7 @@
         <v>0</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="Q18" s="89"/>
     </row>
@@ -6499,7 +6518,7 @@
         <v>1658372.3809523811</v>
       </c>
       <c r="P19" s="17" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Q19" s="89"/>
     </row>
@@ -6514,7 +6533,7 @@
         <v>237</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E20" s="16" t="s">
         <v>79</v>
@@ -6556,7 +6575,7 @@
         <v>2999732.3809523811</v>
       </c>
       <c r="P20" s="17" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q20" s="89">
         <v>1</v>
@@ -6630,7 +6649,7 @@
         <v>247</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>79</v>
@@ -6672,7 +6691,7 @@
         <v>2999732.3809523811</v>
       </c>
       <c r="P22" s="17" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Q22" s="89"/>
     </row>
@@ -6729,7 +6748,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q23" s="89">
         <v>1</v>
@@ -6857,7 +6876,7 @@
         <v>246</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>208</v>
@@ -6902,7 +6921,7 @@
         <v>1658372.3809523811</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q26" s="89">
         <v>1</v>
@@ -6961,7 +6980,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Q27" s="89"/>
     </row>
@@ -7105,7 +7124,7 @@
         <v>1400000</v>
       </c>
       <c r="I30" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="18">
         <f t="shared" si="25"/>
@@ -7117,11 +7136,11 @@
       </c>
       <c r="L30" s="19">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M30" s="18">
         <f t="shared" si="3"/>
-        <v>4784010</v>
+        <v>3189340</v>
       </c>
       <c r="N30" s="18">
         <f t="shared" si="4"/>
@@ -7129,7 +7148,7 @@
       </c>
       <c r="O30" s="18">
         <f t="shared" si="5"/>
-        <v>4784010</v>
+        <v>3189340</v>
       </c>
       <c r="P30" s="17" t="s">
         <v>321</v>
@@ -7198,13 +7217,13 @@
         <v>35</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E32" s="16" t="s">
         <v>79</v>
@@ -7246,7 +7265,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="17" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q32" s="89"/>
     </row>
@@ -7255,13 +7274,13 @@
         <v>35</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E33" s="16" t="s">
         <v>79</v>
@@ -7303,7 +7322,7 @@
         <v>1881932.3809523811</v>
       </c>
       <c r="P33" s="17" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q33" s="89"/>
     </row>
@@ -7312,13 +7331,13 @@
         <v>35</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E34" s="16" t="s">
         <v>79</v>
@@ -7360,7 +7379,7 @@
         <v>1881932.3809523811</v>
       </c>
       <c r="P34" s="17" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="Q34" s="89"/>
     </row>
@@ -7504,7 +7523,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="6">
         <f>SUM(M5:M36)</f>
-        <v>59188510</v>
+        <v>52586270</v>
       </c>
       <c r="N37" s="6">
         <f t="shared" ref="N37:O37" si="37">SUM(N5:N36)</f>
@@ -7512,7 +7531,7 @@
       </c>
       <c r="O37" s="6">
         <f t="shared" si="37"/>
-        <v>59799652.857142851</v>
+        <v>53197412.857142851</v>
       </c>
       <c r="P37" s="7"/>
     </row>
@@ -7544,12 +7563,12 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C41" s="7" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H42" s="5">
         <f>SUMPRODUCT(Q5:Q36,H5:H36)</f>
@@ -7558,7 +7577,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H43" s="5">
         <f>H42*(Ставка_ОПВР+Ставка_ООСМС+Ставка_СН*(1-Ставка_ОПВ-Ставка_ВОСМС))</f>
@@ -7567,7 +7586,7 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C44" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H44" s="6">
         <f>H42+H43</f>
@@ -7576,7 +7595,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -7627,10 +7646,10 @@
         <v>275</v>
       </c>
       <c r="F3" s="103" t="s">
+        <v>519</v>
+      </c>
+      <c r="G3" s="103" t="s">
         <v>520</v>
-      </c>
-      <c r="G3" s="103" t="s">
-        <v>521</v>
       </c>
       <c r="H3" s="25" t="s">
         <v>276</v>
@@ -7653,7 +7672,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>206</v>
@@ -7697,7 +7716,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>206</v>
@@ -7873,13 +7892,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="27" t="s">
+        <v>379</v>
+      </c>
+      <c r="C9" s="27" t="s">
         <v>380</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="D9" s="27" t="s">
         <v>381</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>382</v>
       </c>
       <c r="E9" s="28">
         <v>700000</v>
@@ -7992,7 +8011,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12" s="24" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>
@@ -8014,12 +8033,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -8030,48 +8049,48 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B4" s="93">
         <v>0.1</v>
       </c>
       <c r="C4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B5" s="94">
         <f>Ставка_ОПВР+Ставка_ООСМС+Ставка_СН*(1-Ставка_ОПВ-Ставка_ВОСМС)</f>
         <v>0.1178</v>
       </c>
       <c r="C5" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="95" t="s">
+        <v>501</v>
+      </c>
+      <c r="B7" s="95" t="s">
         <v>502</v>
       </c>
-      <c r="B7" s="95" t="s">
+      <c r="C7" s="95" t="s">
         <v>503</v>
       </c>
-      <c r="C7" s="95" t="s">
+      <c r="D7" s="95" t="s">
         <v>504</v>
       </c>
-      <c r="D7" s="95" t="s">
+      <c r="E7" s="95" t="s">
         <v>505</v>
       </c>
-      <c r="E7" s="95" t="s">
+      <c r="F7" s="95" t="s">
         <v>506</v>
       </c>
-      <c r="F7" s="95" t="s">
+      <c r="G7" s="95" t="s">
         <v>507</v>
-      </c>
-      <c r="G7" s="95" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -8192,48 +8211,48 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="98" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B14" s="97">
         <f>$B$4*(1+$B$5)</f>
         <v>0.11177999999999999</v>
       </c>
       <c r="C14" s="98" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="98" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B15" s="97">
         <f>$B$4*(1+$B$5)*(1+НДС)</f>
         <v>0.12966479999999997</v>
       </c>
       <c r="C15" s="98" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="99" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B18" s="99"/>
       <c r="C18" s="99"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="98" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B19" s="96">
         <f>Аутсорс!E11</f>
@@ -8243,7 +8262,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="98" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B20" s="96">
         <f>Аутсорс!F11</f>
@@ -8253,7 +8272,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="100" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B21" s="101">
         <f>Аутсорс!F11*2</f>
@@ -8263,7 +8282,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="100" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B22" s="101">
         <f>B21*(1+НДС)</f>
@@ -8273,7 +8292,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="98" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B23" s="96">
         <f>Аутсорс!L11</f>
@@ -8283,7 +8302,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
@@ -8332,7 +8351,7 @@
         <v>89</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>90</v>
@@ -8412,7 +8431,7 @@
     </row>
     <row r="8" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C8">
         <f>SUMIFS(Штат!$G$5:$G$36,Штат!$B$5:$B$36,"Департамент социологических*",Штат!$E$5:$E$36,"штат")</f>
@@ -8435,7 +8454,7 @@
     </row>
     <row r="9" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C9">
         <f>SUMIFS(Штат!$G$5:$G$36,Штат!$B$5:$B$36,"Департамент проектного управления*",Штат!$E$5:$E$36,"штат")</f>
@@ -8481,7 +8500,7 @@
     </row>
     <row r="11" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C11">
         <f>SUM(Штат!G22:G29)</f>
@@ -8579,13 +8598,13 @@
         <v>90</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>564</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8611,18 +8630,18 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I57" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
         <v>1800000</v>
       </c>
       <c r="J5" s="5">
-        <f>IF($F5="разово",IF($L5=12,0,$I5),IF($F5="мес",$D5*$E5*(($G5&lt;=1)+($G5&lt;=2)),IF($F5="год",$D5*$E5/12*(($G5&lt;=1)+($G5&lt;=2)),$I5/2)))</f>
+        <f t="shared" ref="J5:J36" si="1">IF($F5="разово",IF($L5=12,0,$I5),IF($F5="мес",$D5*$E5*(($G5&lt;=1)+($G5&lt;=2)),IF($F5="год",$D5*$E5/12*(($G5&lt;=1)+($G5&lt;=2)),$I5/2)))</f>
         <v>1800000</v>
       </c>
       <c r="K5" s="5">
-        <f>IF($F5="разово",IF($L5=12,$I5,0),IF($F5="мес",$D5*$E5*($G5&lt;=3),IF($F5="год",$D5*$E5/12*($G5&lt;=3),$I5/2)))</f>
+        <f t="shared" ref="K5:K36" si="2">IF($F5="разово",IF($L5=12,$I5,0),IF($F5="мес",$D5*$E5*($G5&lt;=3),IF($F5="год",$D5*$E5/12*($G5&lt;=3),$I5/2)))</f>
         <v>0</v>
       </c>
       <c r="L5" s="89">
@@ -8659,11 +8678,11 @@
         <v>900000</v>
       </c>
       <c r="J6" s="5">
-        <f>IF($F6="разово",IF($L6=12,0,$I6),IF($F6="мес",$D6*$E6*(($G6&lt;=1)+($G6&lt;=2)),IF($F6="год",$D6*$E6/12*(($G6&lt;=1)+($G6&lt;=2)),$I6/2)))</f>
+        <f t="shared" si="1"/>
         <v>900000</v>
       </c>
       <c r="K6" s="5">
-        <f>IF($F6="разово",IF($L6=12,$I6,0),IF($F6="мес",$D6*$E6*($G6&lt;=3),IF($F6="год",$D6*$E6/12*($G6&lt;=3),$I6/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L6" s="89">
@@ -8693,18 +8712,18 @@
         <v>1</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="0"/>
         <v>500000</v>
       </c>
       <c r="J7" s="5">
-        <f>IF($F7="разово",IF($L7=12,0,$I7),IF($F7="мес",$D7*$E7*(($G7&lt;=1)+($G7&lt;=2)),IF($F7="год",$D7*$E7/12*(($G7&lt;=1)+($G7&lt;=2)),$I7/2)))</f>
+        <f t="shared" si="1"/>
         <v>500000</v>
       </c>
       <c r="K7" s="5">
-        <f>IF($F7="разово",IF($L7=12,$I7,0),IF($F7="мес",$D7*$E7*($G7&lt;=3),IF($F7="год",$D7*$E7/12*($G7&lt;=3),$I7/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L7" s="89">
@@ -8716,7 +8735,7 @@
         <v>97</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C8" t="s">
         <v>99</v>
@@ -8735,18 +8754,18 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="0"/>
         <v>1394160</v>
       </c>
       <c r="J8" s="5">
-        <f>IF($F8="разово",IF($L8=12,0,$I8),IF($F8="мес",$D8*$E8*(($G8&lt;=1)+($G8&lt;=2)),IF($F8="год",$D8*$E8/12*(($G8&lt;=1)+($G8&lt;=2)),$I8/2)))</f>
+        <f t="shared" si="1"/>
         <v>1394160</v>
       </c>
       <c r="K8" s="5">
-        <f>IF($F8="разово",IF($L8=12,$I8,0),IF($F8="мес",$D8*$E8*($G8&lt;=3),IF($F8="год",$D8*$E8/12*($G8&lt;=3),$I8/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L8" s="89">
@@ -8758,7 +8777,7 @@
         <v>97</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C9" s="80" t="s">
         <v>99</v>
@@ -8777,18 +8796,18 @@
         <v>1</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="I9" s="5">
-        <f t="shared" ref="I9" si="1">IF(F9="разово",IF(G9&lt;=3,D9*E9,0),IF(F9="мес",D9*E9*MAX(0,4-G9),D9*E9*MAX(0,4-G9)/12))</f>
+        <f t="shared" ref="I9" si="3">IF(F9="разово",IF(G9&lt;=3,D9*E9,0),IF(F9="мес",D9*E9*MAX(0,4-G9),D9*E9*MAX(0,4-G9)/12))</f>
         <v>383500</v>
       </c>
       <c r="J9" s="5">
-        <f>IF($F9="разово",IF($L9=12,0,$I9),IF($F9="мес",$D9*$E9*(($G9&lt;=1)+($G9&lt;=2)),IF($F9="год",$D9*$E9/12*(($G9&lt;=1)+($G9&lt;=2)),$I9/2)))</f>
+        <f t="shared" si="1"/>
         <v>383500</v>
       </c>
       <c r="K9" s="5">
-        <f>IF($F9="разово",IF($L9=12,$I9,0),IF($F9="мес",$D9*$E9*($G9&lt;=3),IF($F9="год",$D9*$E9/12*($G9&lt;=3),$I9/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L9" s="89">
@@ -8800,7 +8819,7 @@
         <v>97</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C10" s="81" t="s">
         <v>99</v>
@@ -8819,18 +8838,18 @@
         <v>1</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I10" s="5">
-        <f t="shared" ref="I10" si="2">IF(F10="разово",IF(G10&lt;=3,D10*E10,0),IF(F10="мес",D10*E10*MAX(0,4-G10),D10*E10*MAX(0,4-G10)/12))</f>
+        <f t="shared" ref="I10" si="4">IF(F10="разово",IF(G10&lt;=3,D10*E10,0),IF(F10="мес",D10*E10*MAX(0,4-G10),D10*E10*MAX(0,4-G10)/12))</f>
         <v>244484</v>
       </c>
       <c r="J10" s="5">
-        <f>IF($F10="разово",IF($L10=12,0,$I10),IF($F10="мес",$D10*$E10*(($G10&lt;=1)+($G10&lt;=2)),IF($F10="год",$D10*$E10/12*(($G10&lt;=1)+($G10&lt;=2)),$I10/2)))</f>
+        <f t="shared" si="1"/>
         <v>244484</v>
       </c>
       <c r="K10" s="5">
-        <f>IF($F10="разово",IF($L10=12,$I10,0),IF($F10="мес",$D10*$E10*($G10&lt;=3),IF($F10="год",$D10*$E10/12*($G10&lt;=3),$I10/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L10" s="89">
@@ -8842,7 +8861,7 @@
         <v>97</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C11" s="82" t="s">
         <v>99</v>
@@ -8861,18 +8880,18 @@
         <v>1</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="I11" s="5">
-        <f t="shared" ref="I11" si="3">IF(F11="разово",IF(G11&lt;=3,D11*E11,0),IF(F11="мес",D11*E11*MAX(0,4-G11),D11*E11*MAX(0,4-G11)/12))</f>
+        <f t="shared" ref="I11" si="5">IF(F11="разово",IF(G11&lt;=3,D11*E11,0),IF(F11="мес",D11*E11*MAX(0,4-G11),D11*E11*MAX(0,4-G11)/12))</f>
         <v>98672</v>
       </c>
       <c r="J11" s="5">
-        <f>IF($F11="разово",IF($L11=12,0,$I11),IF($F11="мес",$D11*$E11*(($G11&lt;=1)+($G11&lt;=2)),IF($F11="год",$D11*$E11/12*(($G11&lt;=1)+($G11&lt;=2)),$I11/2)))</f>
+        <f t="shared" si="1"/>
         <v>98672</v>
       </c>
       <c r="K11" s="5">
-        <f>IF($F11="разово",IF($L11=12,$I11,0),IF($F11="мес",$D11*$E11*($G11&lt;=3),IF($F11="год",$D11*$E11/12*($G11&lt;=3),$I11/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L11" s="89">
@@ -8884,7 +8903,7 @@
         <v>97</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C12" t="s">
         <v>99</v>
@@ -8903,18 +8922,18 @@
         <v>1</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J12" s="5">
-        <f>IF($F12="разово",IF($L12=12,0,$I12),IF($F12="мес",$D12*$E12*(($G12&lt;=1)+($G12&lt;=2)),IF($F12="год",$D12*$E12/12*(($G12&lt;=1)+($G12&lt;=2)),$I12/2)))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K12" s="5">
-        <f>IF($F12="разово",IF($L12=12,$I12,0),IF($F12="мес",$D12*$E12*($G12&lt;=3),IF($F12="год",$D12*$E12/12*($G12&lt;=3),$I12/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L12" s="89">
@@ -8926,7 +8945,7 @@
         <v>97</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C13" s="84" t="s">
         <v>99</v>
@@ -8945,18 +8964,18 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="I13" s="5">
         <f>IF(F13="разово",IF(G13&lt;=3,D13*E13,0),IF(F13="мес",D13*E13*MAX(0,4-G13),D13*E13*MAX(0,4-G13)/12))</f>
         <v>39569</v>
       </c>
       <c r="J13" s="5">
-        <f>IF($F13="разово",IF($L13=12,0,$I13),IF($F13="мес",$D13*$E13*(($G13&lt;=1)+($G13&lt;=2)),IF($F13="год",$D13*$E13/12*(($G13&lt;=1)+($G13&lt;=2)),$I13/2)))</f>
+        <f t="shared" si="1"/>
         <v>39569</v>
       </c>
       <c r="K13" s="5">
-        <f>IF($F13="разово",IF($L13=12,$I13,0),IF($F13="мес",$D13*$E13*($G13&lt;=3),IF($F13="год",$D13*$E13/12*($G13&lt;=3),$I13/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L13" s="89">
@@ -8968,7 +8987,7 @@
         <v>97</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C14" s="84" t="s">
         <v>99</v>
@@ -8987,18 +9006,18 @@
         <v>1</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I14" s="5">
         <f>IF(F14="разово",IF(G14&lt;=3,D14*E14,0),IF(F14="мес",D14*E14*MAX(0,4-G14),D14*E14*MAX(0,4-G14)/12))</f>
         <v>0</v>
       </c>
       <c r="J14" s="5">
-        <f>IF($F14="разово",IF($L14=12,0,$I14),IF($F14="мес",$D14*$E14*(($G14&lt;=1)+($G14&lt;=2)),IF($F14="год",$D14*$E14/12*(($G14&lt;=1)+($G14&lt;=2)),$I14/2)))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K14" s="5">
-        <f>IF($F14="разово",IF($L14=12,$I14,0),IF($F14="мес",$D14*$E14*($G14&lt;=3),IF($F14="год",$D14*$E14/12*($G14&lt;=3),$I14/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L14" s="89">
@@ -9010,7 +9029,7 @@
         <v>97</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C15" s="83" t="s">
         <v>99</v>
@@ -9029,18 +9048,18 @@
         <v>1</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="I15" s="5">
-        <f t="shared" ref="I15" si="4">IF(F15="разово",IF(G15&lt;=3,D15*E15,0),IF(F15="мес",D15*E15*MAX(0,4-G15),D15*E15*MAX(0,4-G15)/12))</f>
+        <f t="shared" ref="I15" si="6">IF(F15="разово",IF(G15&lt;=3,D15*E15,0),IF(F15="мес",D15*E15*MAX(0,4-G15),D15*E15*MAX(0,4-G15)/12))</f>
         <v>0</v>
       </c>
       <c r="J15" s="5">
-        <f>IF($F15="разово",IF($L15=12,0,$I15),IF($F15="мес",$D15*$E15*(($G15&lt;=1)+($G15&lt;=2)),IF($F15="год",$D15*$E15/12*(($G15&lt;=1)+($G15&lt;=2)),$I15/2)))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K15" s="5">
-        <f>IF($F15="разово",IF($L15=12,$I15,0),IF($F15="мес",$D15*$E15*($G15&lt;=3),IF($F15="год",$D15*$E15/12*($G15&lt;=3),$I15/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L15" s="89">
@@ -9052,7 +9071,7 @@
         <v>97</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C16" s="92" t="s">
         <v>99</v>
@@ -9071,18 +9090,18 @@
         <v>1</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="I16" s="5">
-        <f t="shared" ref="I16:I21" si="5">IF(F16="разово",IF(G16&lt;=3,D16*E16,0),IF(F16="мес",D16*E16*MAX(0,4-G16),D16*E16*MAX(0,4-G16)/12))</f>
+        <f t="shared" ref="I16:I21" si="7">IF(F16="разово",IF(G16&lt;=3,D16*E16,0),IF(F16="мес",D16*E16*MAX(0,4-G16),D16*E16*MAX(0,4-G16)/12))</f>
         <v>38580</v>
       </c>
       <c r="J16" s="5">
-        <f>IF($F16="разово",IF($L16=12,0,$I16),IF($F16="мес",$D16*$E16*(($G16&lt;=1)+($G16&lt;=2)),IF($F16="год",$D16*$E16/12*(($G16&lt;=1)+($G16&lt;=2)),$I16/2)))</f>
+        <f t="shared" si="1"/>
         <v>38580</v>
       </c>
       <c r="K16" s="5">
-        <f>IF($F16="разово",IF($L16=12,$I16,0),IF($F16="мес",$D16*$E16*($G16&lt;=3),IF($F16="год",$D16*$E16/12*($G16&lt;=3),$I16/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L16" s="89">
@@ -9094,7 +9113,7 @@
         <v>97</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C17" s="87" t="s">
         <v>103</v>
@@ -9113,18 +9132,18 @@
         <v>1</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I17" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>431032</v>
       </c>
       <c r="J17" s="5">
-        <f>IF($F17="разово",IF($L17=12,0,$I17),IF($F17="мес",$D17*$E17*(($G17&lt;=1)+($G17&lt;=2)),IF($F17="год",$D17*$E17/12*(($G17&lt;=1)+($G17&lt;=2)),$I17/2)))</f>
+        <f t="shared" si="1"/>
         <v>431032</v>
       </c>
       <c r="K17" s="5">
-        <f>IF($F17="разово",IF($L17=12,$I17,0),IF($F17="мес",$D17*$E17*($G17&lt;=3),IF($F17="год",$D17*$E17/12*($G17&lt;=3),$I17/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L17" s="89">
@@ -9136,7 +9155,7 @@
         <v>97</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C18" s="91" t="s">
         <v>103</v>
@@ -9155,18 +9174,18 @@
         <v>1</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="I18" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>456896</v>
       </c>
       <c r="J18" s="5">
-        <f>IF($F18="разово",IF($L18=12,0,$I18),IF($F18="мес",$D18*$E18*(($G18&lt;=1)+($G18&lt;=2)),IF($F18="год",$D18*$E18/12*(($G18&lt;=1)+($G18&lt;=2)),$I18/2)))</f>
+        <f t="shared" si="1"/>
         <v>456896</v>
       </c>
       <c r="K18" s="5">
-        <f>IF($F18="разово",IF($L18=12,$I18,0),IF($F18="мес",$D18*$E18*($G18&lt;=3),IF($F18="год",$D18*$E18/12*($G18&lt;=3),$I18/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L18" s="89">
@@ -9178,7 +9197,7 @@
         <v>97</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C19" s="85" t="s">
         <v>99</v>
@@ -9197,18 +9216,18 @@
         <v>1</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I19" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>69582</v>
       </c>
       <c r="J19" s="5">
-        <f>IF($F19="разово",IF($L19=12,0,$I19),IF($F19="мес",$D19*$E19*(($G19&lt;=1)+($G19&lt;=2)),IF($F19="год",$D19*$E19/12*(($G19&lt;=1)+($G19&lt;=2)),$I19/2)))</f>
+        <f t="shared" si="1"/>
         <v>69582</v>
       </c>
       <c r="K19" s="5">
-        <f>IF($F19="разово",IF($L19=12,$I19,0),IF($F19="мес",$D19*$E19*($G19&lt;=3),IF($F19="год",$D19*$E19/12*($G19&lt;=3),$I19/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L19" s="89">
@@ -9220,7 +9239,7 @@
         <v>97</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C20" s="86" t="s">
         <v>103</v>
@@ -9239,18 +9258,18 @@
         <v>1</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="I20" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>102466</v>
       </c>
       <c r="J20" s="5">
-        <f>IF($F20="разово",IF($L20=12,0,$I20),IF($F20="мес",$D20*$E20*(($G20&lt;=1)+($G20&lt;=2)),IF($F20="год",$D20*$E20/12*(($G20&lt;=1)+($G20&lt;=2)),$I20/2)))</f>
+        <f t="shared" si="1"/>
         <v>102466</v>
       </c>
       <c r="K20" s="5">
-        <f>IF($F20="разово",IF($L20=12,$I20,0),IF($F20="мес",$D20*$E20*($G20&lt;=3),IF($F20="год",$D20*$E20/12*($G20&lt;=3),$I20/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L20" s="89">
@@ -9262,7 +9281,7 @@
         <v>97</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C21" s="86" t="s">
         <v>103</v>
@@ -9281,18 +9300,18 @@
         <v>1</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I21" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>31888</v>
       </c>
       <c r="J21" s="5">
-        <f>IF($F21="разово",IF($L21=12,0,$I21),IF($F21="мес",$D21*$E21*(($G21&lt;=1)+($G21&lt;=2)),IF($F21="год",$D21*$E21/12*(($G21&lt;=1)+($G21&lt;=2)),$I21/2)))</f>
+        <f t="shared" si="1"/>
         <v>31888</v>
       </c>
       <c r="K21" s="5">
-        <f>IF($F21="разово",IF($L21=12,$I21,0),IF($F21="мес",$D21*$E21*($G21&lt;=3),IF($F21="год",$D21*$E21/12*($G21&lt;=3),$I21/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L21" s="89">
@@ -9327,11 +9346,11 @@
         <v>0</v>
       </c>
       <c r="J22" s="5">
-        <f>IF($F22="разово",IF($L22=12,0,$I22),IF($F22="мес",$D22*$E22*(($G22&lt;=1)+($G22&lt;=2)),IF($F22="год",$D22*$E22/12*(($G22&lt;=1)+($G22&lt;=2)),$I22/2)))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K22" s="5">
-        <f>IF($F22="разово",IF($L22=12,$I22,0),IF($F22="мес",$D22*$E22*($G22&lt;=3),IF($F22="год",$D22*$E22/12*($G22&lt;=3),$I22/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L22" s="89">
@@ -9343,7 +9362,7 @@
         <v>97</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C23" t="s">
         <v>103</v>
@@ -9366,11 +9385,11 @@
         <v>0</v>
       </c>
       <c r="J23" s="5">
-        <f>IF($F23="разово",IF($L23=12,0,$I23),IF($F23="мес",$D23*$E23*(($G23&lt;=1)+($G23&lt;=2)),IF($F23="год",$D23*$E23/12*(($G23&lt;=1)+($G23&lt;=2)),$I23/2)))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K23" s="5">
-        <f>IF($F23="разово",IF($L23=12,$I23,0),IF($F23="мес",$D23*$E23*($G23&lt;=3),IF($F23="год",$D23*$E23/12*($G23&lt;=3),$I23/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L23" s="89">
@@ -9382,7 +9401,7 @@
         <v>97</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C24" t="s">
         <v>103</v>
@@ -9400,18 +9419,18 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J24" s="5">
-        <f>IF($F24="разово",IF($L24=12,0,$I24),IF($F24="мес",$D24*$E24*(($G24&lt;=1)+($G24&lt;=2)),IF($F24="год",$D24*$E24/12*(($G24&lt;=1)+($G24&lt;=2)),$I24/2)))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K24" s="5">
-        <f>IF($F24="разово",IF($L24=12,$I24,0),IF($F24="мес",$D24*$E24*($G24&lt;=3),IF($F24="год",$D24*$E24/12*($G24&lt;=3),$I24/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L24" s="89">
@@ -9448,11 +9467,11 @@
         <v>0</v>
       </c>
       <c r="J25" s="5">
-        <f>IF($F25="разово",IF($L25=12,0,$I25),IF($F25="мес",$D25*$E25*(($G25&lt;=1)+($G25&lt;=2)),IF($F25="год",$D25*$E25/12*(($G25&lt;=1)+($G25&lt;=2)),$I25/2)))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K25" s="5">
-        <f>IF($F25="разово",IF($L25=12,$I25,0),IF($F25="мес",$D25*$E25*($G25&lt;=3),IF($F25="год",$D25*$E25/12*($G25&lt;=3),$I25/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L25" s="89">
@@ -9490,11 +9509,11 @@
         <v>329082.90000000002</v>
       </c>
       <c r="J26" s="5">
-        <f>IF($F26="разово",IF($L26=12,0,$I26),IF($F26="мес",$D26*$E26*(($G26&lt;=1)+($G26&lt;=2)),IF($F26="год",$D26*$E26/12*(($G26&lt;=1)+($G26&lt;=2)),$I26/2)))</f>
+        <f t="shared" si="1"/>
         <v>329082.90000000002</v>
       </c>
       <c r="K26" s="5">
-        <f>IF($F26="разово",IF($L26=12,$I26,0),IF($F26="мес",$D26*$E26*($G26&lt;=3),IF($F26="год",$D26*$E26/12*($G26&lt;=3),$I26/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L26" s="89">
@@ -9506,7 +9525,7 @@
         <v>97</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C27" s="86" t="s">
         <v>103</v>
@@ -9525,18 +9544,18 @@
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="I27" s="5">
         <f>IF(F27="разово",IF(G27&lt;=3,D27*E27,0),IF(F27="мес",D27*E27*MAX(0,4-G27),D27*E27*MAX(0,4-G27)/12))</f>
         <v>21552</v>
       </c>
       <c r="J27" s="5">
-        <f>IF($F27="разово",IF($L27=12,0,$I27),IF($F27="мес",$D27*$E27*(($G27&lt;=1)+($G27&lt;=2)),IF($F27="год",$D27*$E27/12*(($G27&lt;=1)+($G27&lt;=2)),$I27/2)))</f>
+        <f t="shared" si="1"/>
         <v>21552</v>
       </c>
       <c r="K27" s="5">
-        <f>IF($F27="разово",IF($L27=12,$I27,0),IF($F27="мес",$D27*$E27*($G27&lt;=3),IF($F27="год",$D27*$E27/12*($G27&lt;=3),$I27/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L27" s="89">
@@ -9573,11 +9592,11 @@
         <v>2500000</v>
       </c>
       <c r="J28" s="5">
-        <f>IF($F28="разово",IF($L28=12,0,$I28),IF($F28="мес",$D28*$E28*(($G28&lt;=1)+($G28&lt;=2)),IF($F28="год",$D28*$E28/12*(($G28&lt;=1)+($G28&lt;=2)),$I28/2)))</f>
+        <f t="shared" si="1"/>
         <v>2500000</v>
       </c>
       <c r="K28" s="5">
-        <f>IF($F28="разово",IF($L28=12,$I28,0),IF($F28="мес",$D28*$E28*($G28&lt;=3),IF($F28="год",$D28*$E28/12*($G28&lt;=3),$I28/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L28" s="89">
@@ -9612,11 +9631,11 @@
         <v>300000</v>
       </c>
       <c r="J29" s="5">
-        <f>IF($F29="разово",IF($L29=12,0,$I29),IF($F29="мес",$D29*$E29*(($G29&lt;=1)+($G29&lt;=2)),IF($F29="год",$D29*$E29/12*(($G29&lt;=1)+($G29&lt;=2)),$I29/2)))</f>
+        <f t="shared" si="1"/>
         <v>300000</v>
       </c>
       <c r="K29" s="5">
-        <f>IF($F29="разово",IF($L29=12,$I29,0),IF($F29="мес",$D29*$E29*($G29&lt;=3),IF($F29="год",$D29*$E29/12*($G29&lt;=3),$I29/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L29" s="89">
@@ -9653,11 +9672,11 @@
         <v>560000</v>
       </c>
       <c r="J30" s="5">
-        <f>IF($F30="разово",IF($L30=12,0,$I30),IF($F30="мес",$D30*$E30*(($G30&lt;=1)+($G30&lt;=2)),IF($F30="год",$D30*$E30/12*(($G30&lt;=1)+($G30&lt;=2)),$I30/2)))</f>
+        <f t="shared" si="1"/>
         <v>560000</v>
       </c>
       <c r="K30" s="5">
-        <f>IF($F30="разово",IF($L30=12,$I30,0),IF($F30="мес",$D30*$E30*($G30&lt;=3),IF($F30="год",$D30*$E30/12*($G30&lt;=3),$I30/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L30" s="89">
@@ -9694,11 +9713,11 @@
         <v>220000</v>
       </c>
       <c r="J31" s="5">
-        <f>IF($F31="разово",IF($L31=12,0,$I31),IF($F31="мес",$D31*$E31*(($G31&lt;=1)+($G31&lt;=2)),IF($F31="год",$D31*$E31/12*(($G31&lt;=1)+($G31&lt;=2)),$I31/2)))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K31" s="5">
-        <f>IF($F31="разово",IF($L31=12,$I31,0),IF($F31="мес",$D31*$E31*($G31&lt;=3),IF($F31="год",$D31*$E31/12*($G31&lt;=3),$I31/2)))</f>
+        <f t="shared" si="2"/>
         <v>220000</v>
       </c>
       <c r="L31" s="89">
@@ -9735,11 +9754,11 @@
         <v>300000</v>
       </c>
       <c r="J32" s="5">
-        <f>IF($F32="разово",IF($L32=12,0,$I32),IF($F32="мес",$D32*$E32*(($G32&lt;=1)+($G32&lt;=2)),IF($F32="год",$D32*$E32/12*(($G32&lt;=1)+($G32&lt;=2)),$I32/2)))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K32" s="5">
-        <f>IF($F32="разово",IF($L32=12,$I32,0),IF($F32="мес",$D32*$E32*($G32&lt;=3),IF($F32="год",$D32*$E32/12*($G32&lt;=3),$I32/2)))</f>
+        <f t="shared" si="2"/>
         <v>300000</v>
       </c>
       <c r="L32" s="89">
@@ -9775,11 +9794,11 @@
         <v>0</v>
       </c>
       <c r="J33" s="5">
-        <f>IF($F33="разово",IF($L33=12,0,$I33),IF($F33="мес",$D33*$E33*(($G33&lt;=1)+($G33&lt;=2)),IF($F33="год",$D33*$E33/12*(($G33&lt;=1)+($G33&lt;=2)),$I33/2)))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K33" s="5">
-        <f>IF($F33="разово",IF($L33=12,$I33,0),IF($F33="мес",$D33*$E33*($G33&lt;=3),IF($F33="год",$D33*$E33/12*($G33&lt;=3),$I33/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L33" s="89">
@@ -9815,11 +9834,11 @@
         <v>0</v>
       </c>
       <c r="J34" s="5">
-        <f>IF($F34="разово",IF($L34=12,0,$I34),IF($F34="мес",$D34*$E34*(($G34&lt;=1)+($G34&lt;=2)),IF($F34="год",$D34*$E34/12*(($G34&lt;=1)+($G34&lt;=2)),$I34/2)))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K34" s="5">
-        <f>IF($F34="разово",IF($L34=12,$I34,0),IF($F34="мес",$D34*$E34*($G34&lt;=3),IF($F34="год",$D34*$E34/12*($G34&lt;=3),$I34/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L34" s="89">
@@ -9855,11 +9874,11 @@
         <v>0</v>
       </c>
       <c r="J35" s="5">
-        <f>IF($F35="разово",IF($L35=12,0,$I35),IF($F35="мес",$D35*$E35*(($G35&lt;=1)+($G35&lt;=2)),IF($F35="год",$D35*$E35/12*(($G35&lt;=1)+($G35&lt;=2)),$I35/2)))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K35" s="5">
-        <f>IF($F35="разово",IF($L35=12,$I35,0),IF($F35="мес",$D35*$E35*($G35&lt;=3),IF($F35="год",$D35*$E35/12*($G35&lt;=3),$I35/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L35" s="89">
@@ -9895,11 +9914,11 @@
         <v>0</v>
       </c>
       <c r="J36" s="5">
-        <f>IF($F36="разово",IF($L36=12,0,$I36),IF($F36="мес",$D36*$E36*(($G36&lt;=1)+($G36&lt;=2)),IF($F36="год",$D36*$E36/12*(($G36&lt;=1)+($G36&lt;=2)),$I36/2)))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K36" s="5">
-        <f>IF($F36="разово",IF($L36=12,$I36,0),IF($F36="мес",$D36*$E36*($G36&lt;=3),IF($F36="год",$D36*$E36/12*($G36&lt;=3),$I36/2)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L36" s="89">
@@ -9930,18 +9949,18 @@
         <v>1</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="0"/>
         <v>74550</v>
       </c>
       <c r="J37" s="5">
-        <f>IF($F37="разово",IF($L37=12,0,$I37),IF($F37="мес",$D37*$E37*(($G37&lt;=1)+($G37&lt;=2)),IF($F37="год",$D37*$E37/12*(($G37&lt;=1)+($G37&lt;=2)),$I37/2)))</f>
+        <f t="shared" ref="J37:J57" si="8">IF($F37="разово",IF($L37=12,0,$I37),IF($F37="мес",$D37*$E37*(($G37&lt;=1)+($G37&lt;=2)),IF($F37="год",$D37*$E37/12*(($G37&lt;=1)+($G37&lt;=2)),$I37/2)))</f>
         <v>74550</v>
       </c>
       <c r="K37" s="5">
-        <f>IF($F37="разово",IF($L37=12,$I37,0),IF($F37="мес",$D37*$E37*($G37&lt;=3),IF($F37="год",$D37*$E37/12*($G37&lt;=3),$I37/2)))</f>
+        <f t="shared" ref="K37:K68" si="9">IF($F37="разово",IF($L37=12,$I37,0),IF($F37="мес",$D37*$E37*($G37&lt;=3),IF($F37="год",$D37*$E37/12*($G37&lt;=3),$I37/2)))</f>
         <v>0</v>
       </c>
       <c r="L37" s="89">
@@ -9972,18 +9991,18 @@
         <v>1</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="0"/>
         <v>15777</v>
       </c>
       <c r="J38" s="5">
-        <f>IF($F38="разово",IF($L38=12,0,$I38),IF($F38="мес",$D38*$E38*(($G38&lt;=1)+($G38&lt;=2)),IF($F38="год",$D38*$E38/12*(($G38&lt;=1)+($G38&lt;=2)),$I38/2)))</f>
+        <f t="shared" si="8"/>
         <v>15777</v>
       </c>
       <c r="K38" s="5">
-        <f>IF($F38="разово",IF($L38=12,$I38,0),IF($F38="мес",$D38*$E38*($G38&lt;=3),IF($F38="год",$D38*$E38/12*($G38&lt;=3),$I38/2)))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L38" s="89">
@@ -10021,11 +10040,11 @@
         <v>24948</v>
       </c>
       <c r="J39" s="5">
-        <f>IF($F39="разово",IF($L39=12,0,$I39),IF($F39="мес",$D39*$E39*(($G39&lt;=1)+($G39&lt;=2)),IF($F39="год",$D39*$E39/12*(($G39&lt;=1)+($G39&lt;=2)),$I39/2)))</f>
+        <f t="shared" si="8"/>
         <v>24948</v>
       </c>
       <c r="K39" s="5">
-        <f>IF($F39="разово",IF($L39=12,$I39,0),IF($F39="мес",$D39*$E39*($G39&lt;=3),IF($F39="год",$D39*$E39/12*($G39&lt;=3),$I39/2)))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L39" s="89">
@@ -10063,11 +10082,11 @@
         <v>77920</v>
       </c>
       <c r="J40" s="5">
-        <f>IF($F40="разово",IF($L40=12,0,$I40),IF($F40="мес",$D40*$E40*(($G40&lt;=1)+($G40&lt;=2)),IF($F40="год",$D40*$E40/12*(($G40&lt;=1)+($G40&lt;=2)),$I40/2)))</f>
+        <f t="shared" si="8"/>
         <v>77920</v>
       </c>
       <c r="K40" s="5">
-        <f>IF($F40="разово",IF($L40=12,$I40,0),IF($F40="мес",$D40*$E40*($G40&lt;=3),IF($F40="год",$D40*$E40/12*($G40&lt;=3),$I40/2)))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L40" s="89">
@@ -10101,15 +10120,15 @@
         <v>307</v>
       </c>
       <c r="I41" s="5">
-        <f t="shared" ref="I41" si="6">IF(F41="разово",IF(G41&lt;=3,D41*E41,0),IF(F41="мес",D41*E41*MAX(0,4-G41),D41*E41*MAX(0,4-G41)/12))</f>
+        <f t="shared" ref="I41" si="10">IF(F41="разово",IF(G41&lt;=3,D41*E41,0),IF(F41="мес",D41*E41*MAX(0,4-G41),D41*E41*MAX(0,4-G41)/12))</f>
         <v>769840</v>
       </c>
       <c r="J41" s="5">
-        <f>IF($F41="разово",IF($L41=12,0,$I41),IF($F41="мес",$D41*$E41*(($G41&lt;=1)+($G41&lt;=2)),IF($F41="год",$D41*$E41/12*(($G41&lt;=1)+($G41&lt;=2)),$I41/2)))</f>
+        <f t="shared" si="8"/>
         <v>769840</v>
       </c>
       <c r="K41" s="5">
-        <f>IF($F41="разово",IF($L41=12,$I41,0),IF($F41="мес",$D41*$E41*($G41&lt;=3),IF($F41="год",$D41*$E41/12*($G41&lt;=3),$I41/2)))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L41" s="89">
@@ -10121,7 +10140,7 @@
         <v>97</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C42" s="105" t="s">
         <v>99</v>
@@ -10140,18 +10159,18 @@
         <v>1</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="I42" s="5">
         <f>IF(F42="разово",IF(G42&lt;=3,D42*E42,0),IF(F42="мес",D42*E42*MAX(0,4-G42),D42*E42*MAX(0,4-G42)/12))</f>
         <v>31240</v>
       </c>
       <c r="J42" s="5">
-        <f>IF($F42="разово",IF($L42=12,0,$I42),IF($F42="мес",$D42*$E42*(($G42&lt;=1)+($G42&lt;=2)),IF($F42="год",$D42*$E42/12*(($G42&lt;=1)+($G42&lt;=2)),$I42/2)))</f>
+        <f t="shared" si="8"/>
         <v>31240</v>
       </c>
       <c r="K42" s="5">
-        <f>IF($F42="разово",IF($L42=12,$I42,0),IF($F42="мес",$D42*$E42*($G42&lt;=3),IF($F42="год",$D42*$E42/12*($G42&lt;=3),$I42/2)))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L42" s="89">
@@ -10189,11 +10208,11 @@
         <v>0</v>
       </c>
       <c r="J43" s="5">
-        <f>IF($F43="разово",IF($L43=12,0,$I43),IF($F43="мес",$D43*$E43*(($G43&lt;=1)+($G43&lt;=2)),IF($F43="год",$D43*$E43/12*(($G43&lt;=1)+($G43&lt;=2)),$I43/2)))</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K43" s="5">
-        <f>IF($F43="разово",IF($L43=12,$I43,0),IF($F43="мес",$D43*$E43*($G43&lt;=3),IF($F43="год",$D43*$E43/12*($G43&lt;=3),$I43/2)))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L43" s="89">
@@ -10205,7 +10224,7 @@
         <v>97</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C44" t="s">
         <v>99</v>
@@ -10224,18 +10243,18 @@
         <v>1</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="I44" s="5">
         <f t="shared" si="0"/>
         <v>49129</v>
       </c>
       <c r="J44" s="5">
-        <f>IF($F44="разово",IF($L44=12,0,$I44),IF($F44="мес",$D44*$E44*(($G44&lt;=1)+($G44&lt;=2)),IF($F44="год",$D44*$E44/12*(($G44&lt;=1)+($G44&lt;=2)),$I44/2)))</f>
+        <f t="shared" si="8"/>
         <v>49129</v>
       </c>
       <c r="K44" s="5">
-        <f>IF($F44="разово",IF($L44=12,$I44,0),IF($F44="мес",$D44*$E44*($G44&lt;=3),IF($F44="год",$D44*$E44/12*($G44&lt;=3),$I44/2)))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L44" s="89">
@@ -10247,7 +10266,7 @@
         <v>97</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C45" s="90" t="s">
         <v>99</v>
@@ -10266,18 +10285,18 @@
         <v>1</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="I45" s="5">
         <f>IF(F45="разово",IF(G45&lt;=3,D45*E45,0),IF(F45="мес",D45*E45*MAX(0,4-G45),D45*E45*MAX(0,4-G45)/12))</f>
         <v>96211</v>
       </c>
       <c r="J45" s="5">
-        <f>IF($F45="разово",IF($L45=12,0,$I45),IF($F45="мес",$D45*$E45*(($G45&lt;=1)+($G45&lt;=2)),IF($F45="год",$D45*$E45/12*(($G45&lt;=1)+($G45&lt;=2)),$I45/2)))</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K45" s="5">
-        <f>IF($F45="разово",IF($L45=12,$I45,0),IF($F45="мес",$D45*$E45*($G45&lt;=3),IF($F45="год",$D45*$E45/12*($G45&lt;=3),$I45/2)))</f>
+        <f t="shared" si="9"/>
         <v>96211</v>
       </c>
       <c r="L45" s="89">
@@ -10289,7 +10308,7 @@
         <v>97</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C46" t="s">
         <v>103</v>
@@ -10307,18 +10326,18 @@
         <v>1</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="0"/>
         <v>300000</v>
       </c>
       <c r="J46" s="5">
-        <f>IF($F46="разово",IF($L46=12,0,$I46),IF($F46="мес",$D46*$E46*(($G46&lt;=1)+($G46&lt;=2)),IF($F46="год",$D46*$E46/12*(($G46&lt;=1)+($G46&lt;=2)),$I46/2)))</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K46" s="5">
-        <f>IF($F46="разово",IF($L46=12,$I46,0),IF($F46="мес",$D46*$E46*($G46&lt;=3),IF($F46="год",$D46*$E46/12*($G46&lt;=3),$I46/2)))</f>
+        <f t="shared" si="9"/>
         <v>300000</v>
       </c>
       <c r="L46" s="89">
@@ -10355,11 +10374,11 @@
         <v>0</v>
       </c>
       <c r="J47" s="5">
-        <f>IF($F47="разово",IF($L47=12,0,$I47),IF($F47="мес",$D47*$E47*(($G47&lt;=1)+($G47&lt;=2)),IF($F47="год",$D47*$E47/12*(($G47&lt;=1)+($G47&lt;=2)),$I47/2)))</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K47" s="5">
-        <f>IF($F47="разово",IF($L47=12,$I47,0),IF($F47="мес",$D47*$E47*($G47&lt;=3),IF($F47="год",$D47*$E47/12*($G47&lt;=3),$I47/2)))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L47" s="89">
@@ -10394,11 +10413,11 @@
         <v>0</v>
       </c>
       <c r="J48" s="5">
-        <f>IF($F48="разово",IF($L48=12,0,$I48),IF($F48="мес",$D48*$E48*(($G48&lt;=1)+($G48&lt;=2)),IF($F48="год",$D48*$E48/12*(($G48&lt;=1)+($G48&lt;=2)),$I48/2)))</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K48" s="5">
-        <f>IF($F48="разово",IF($L48=12,$I48,0),IF($F48="мес",$D48*$E48*($G48&lt;=3),IF($F48="год",$D48*$E48/12*($G48&lt;=3),$I48/2)))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L48" s="89">
@@ -10410,7 +10429,7 @@
         <v>97</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C49" t="s">
         <v>108</v>
@@ -10429,18 +10448,18 @@
         <v>1</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I49" s="5">
         <f t="shared" si="0"/>
         <v>300000</v>
       </c>
       <c r="J49" s="5">
-        <f>IF($F49="разово",IF($L49=12,0,$I49),IF($F49="мес",$D49*$E49*(($G49&lt;=1)+($G49&lt;=2)),IF($F49="год",$D49*$E49/12*(($G49&lt;=1)+($G49&lt;=2)),$I49/2)))</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K49" s="5">
-        <f>IF($F49="разово",IF($L49=12,$I49,0),IF($F49="мес",$D49*$E49*($G49&lt;=3),IF($F49="год",$D49*$E49/12*($G49&lt;=3),$I49/2)))</f>
+        <f t="shared" si="9"/>
         <v>300000</v>
       </c>
       <c r="L49" s="89">
@@ -10475,11 +10494,11 @@
         <v>400000</v>
       </c>
       <c r="J50" s="5">
-        <f>IF($F50="разово",IF($L50=12,0,$I50),IF($F50="мес",$D50*$E50*(($G50&lt;=1)+($G50&lt;=2)),IF($F50="год",$D50*$E50/12*(($G50&lt;=1)+($G50&lt;=2)),$I50/2)))</f>
+        <f t="shared" si="8"/>
         <v>400000</v>
       </c>
       <c r="K50" s="5">
-        <f>IF($F50="разово",IF($L50=12,$I50,0),IF($F50="мес",$D50*$E50*($G50&lt;=3),IF($F50="год",$D50*$E50/12*($G50&lt;=3),$I50/2)))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L50" s="89">
@@ -10513,15 +10532,15 @@
         <v>313</v>
       </c>
       <c r="I51" s="5">
-        <f t="shared" ref="I51" si="7">IF(F51="разово",IF(G51&lt;=3,D51*E51,0),IF(F51="мес",D51*E51*MAX(0,4-G51),D51*E51*MAX(0,4-G51)/12))</f>
+        <f t="shared" ref="I51" si="11">IF(F51="разово",IF(G51&lt;=3,D51*E51,0),IF(F51="мес",D51*E51*MAX(0,4-G51),D51*E51*MAX(0,4-G51)/12))</f>
         <v>31026</v>
       </c>
       <c r="J51" s="5">
-        <f>IF($F51="разово",IF($L51=12,0,$I51),IF($F51="мес",$D51*$E51*(($G51&lt;=1)+($G51&lt;=2)),IF($F51="год",$D51*$E51/12*(($G51&lt;=1)+($G51&lt;=2)),$I51/2)))</f>
+        <f t="shared" si="8"/>
         <v>31026</v>
       </c>
       <c r="K51" s="5">
-        <f>IF($F51="разово",IF($L51=12,$I51,0),IF($F51="мес",$D51*$E51*($G51&lt;=3),IF($F51="год",$D51*$E51/12*($G51&lt;=3),$I51/2)))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L51" s="89">
@@ -10533,7 +10552,7 @@
         <v>97</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C52" t="s">
         <v>99</v>
@@ -10552,18 +10571,18 @@
         <v>1</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I52" s="5">
-        <f t="shared" ref="I52:I54" si="8">IF(F52="разово",IF(G52&lt;=3,D52*E52,0),IF(F52="мес",D52*E52*MAX(0,4-G52),D52*E52*MAX(0,4-G52)/12))</f>
+        <f t="shared" ref="I52:I54" si="12">IF(F52="разово",IF(G52&lt;=3,D52*E52,0),IF(F52="мес",D52*E52*MAX(0,4-G52),D52*E52*MAX(0,4-G52)/12))</f>
         <v>130940</v>
       </c>
       <c r="J52" s="5">
-        <f>IF($F52="разово",IF($L52=12,0,$I52),IF($F52="мес",$D52*$E52*(($G52&lt;=1)+($G52&lt;=2)),IF($F52="год",$D52*$E52/12*(($G52&lt;=1)+($G52&lt;=2)),$I52/2)))</f>
+        <f t="shared" si="8"/>
         <v>130940</v>
       </c>
       <c r="K52" s="5">
-        <f>IF($F52="разово",IF($L52=12,$I52,0),IF($F52="мес",$D52*$E52*($G52&lt;=3),IF($F52="год",$D52*$E52/12*($G52&lt;=3),$I52/2)))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L52" s="89">
@@ -10575,7 +10594,7 @@
         <v>97</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C53" t="s">
         <v>103</v>
@@ -10594,18 +10613,18 @@
         <v>1</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I53" s="5">
+        <f t="shared" si="12"/>
+        <v>369600</v>
+      </c>
+      <c r="J53" s="5">
         <f t="shared" si="8"/>
         <v>369600</v>
       </c>
-      <c r="J53" s="5">
-        <f>IF($F53="разово",IF($L53=12,0,$I53),IF($F53="мес",$D53*$E53*(($G53&lt;=1)+($G53&lt;=2)),IF($F53="год",$D53*$E53/12*(($G53&lt;=1)+($G53&lt;=2)),$I53/2)))</f>
-        <v>369600</v>
-      </c>
       <c r="K53" s="5">
-        <f>IF($F53="разово",IF($L53=12,$I53,0),IF($F53="мес",$D53*$E53*($G53&lt;=3),IF($F53="год",$D53*$E53/12*($G53&lt;=3),$I53/2)))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L53" s="89">
@@ -10617,7 +10636,7 @@
         <v>97</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C54" t="s">
         <v>99</v>
@@ -10636,18 +10655,18 @@
         <v>1</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I54" s="5">
+        <f t="shared" si="12"/>
+        <v>79398</v>
+      </c>
+      <c r="J54" s="5">
         <f t="shared" si="8"/>
-        <v>79398</v>
-      </c>
-      <c r="J54" s="5">
-        <f>IF($F54="разово",IF($L54=12,0,$I54),IF($F54="мес",$D54*$E54*(($G54&lt;=1)+($G54&lt;=2)),IF($F54="год",$D54*$E54/12*(($G54&lt;=1)+($G54&lt;=2)),$I54/2)))</f>
         <v>0</v>
       </c>
       <c r="K54" s="5">
-        <f>IF($F54="разово",IF($L54=12,$I54,0),IF($F54="мес",$D54*$E54*($G54&lt;=3),IF($F54="год",$D54*$E54/12*($G54&lt;=3),$I54/2)))</f>
+        <f t="shared" si="9"/>
         <v>79398</v>
       </c>
       <c r="L54" s="89">
@@ -10682,11 +10701,11 @@
         <v>150000</v>
       </c>
       <c r="J55" s="5">
-        <f>IF($F55="разово",IF($L55=12,0,$I55),IF($F55="мес",$D55*$E55*(($G55&lt;=1)+($G55&lt;=2)),IF($F55="год",$D55*$E55/12*(($G55&lt;=1)+($G55&lt;=2)),$I55/2)))</f>
+        <f t="shared" si="8"/>
         <v>150000</v>
       </c>
       <c r="K55" s="5">
-        <f>IF($F55="разово",IF($L55=12,$I55,0),IF($F55="мес",$D55*$E55*($G55&lt;=3),IF($F55="год",$D55*$E55/12*($G55&lt;=3),$I55/2)))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L55" s="89">
@@ -10721,11 +10740,11 @@
         <v>400000</v>
       </c>
       <c r="J56" s="5">
-        <f>IF($F56="разово",IF($L56=12,0,$I56),IF($F56="мес",$D56*$E56*(($G56&lt;=1)+($G56&lt;=2)),IF($F56="год",$D56*$E56/12*(($G56&lt;=1)+($G56&lt;=2)),$I56/2)))</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K56" s="5">
-        <f>IF($F56="разово",IF($L56=12,$I56,0),IF($F56="мес",$D56*$E56*($G56&lt;=3),IF($F56="год",$D56*$E56/12*($G56&lt;=3),$I56/2)))</f>
+        <f t="shared" si="9"/>
         <v>400000</v>
       </c>
       <c r="L56" s="89">
@@ -10737,7 +10756,7 @@
         <v>97</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C57" t="s">
         <v>99</v>
@@ -10760,11 +10779,11 @@
         <v>10000</v>
       </c>
       <c r="J57" s="5">
-        <f>IF($F57="разово",IF($L57=12,0,$I57),IF($F57="мес",$D57*$E57*(($G57&lt;=1)+($G57&lt;=2)),IF($F57="год",$D57*$E57/12*(($G57&lt;=1)+($G57&lt;=2)),$I57/2)))</f>
+        <f t="shared" si="8"/>
         <v>10000</v>
       </c>
       <c r="K57" s="5">
-        <f>IF($F57="разово",IF($L57=12,$I57,0),IF($F57="мес",$D57*$E57*($G57&lt;=3),IF($F57="год",$D57*$E57/12*($G57&lt;=3),$I57/2)))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L57" s="89">
@@ -10806,7 +10825,7 @@
         <v>6596915.7483870964</v>
       </c>
       <c r="K58" s="5">
-        <f>IF($F58="разово",IF($L58=12,$I58,0),IF($F58="мес",$D58*$E58*($G58&lt;=3),IF($F58="год",$D58*$E58/12*($G58&lt;=3),$I58/2)))</f>
+        <f t="shared" si="9"/>
         <v>4869152.0999999996</v>
       </c>
       <c r="L58" s="89"/>
@@ -10838,15 +10857,15 @@
         <v>256</v>
       </c>
       <c r="I59" s="5">
-        <f t="shared" ref="I59:I77" si="9">IF(F59="разово",IF(G59&lt;=3,D59*E59,0),IF(F59="мес",D59*E59*MAX(0,4-G59),D59*E59*MAX(0,4-G59)/12))</f>
+        <f t="shared" ref="I59:I77" si="13">IF(F59="разово",IF(G59&lt;=3,D59*E59,0),IF(F59="мес",D59*E59*MAX(0,4-G59),D59*E59*MAX(0,4-G59)/12))</f>
         <v>4869152.0999999996</v>
       </c>
       <c r="J59" s="5">
-        <f>IF($F59="разово",IF($L59=12,0,$I59),IF($F59="мес",$D59*$E59*(($G59&lt;=1)+($G59&lt;=2)),IF($F59="год",$D59*$E59/12*(($G59&lt;=1)+($G59&lt;=2)),$I59/2)))</f>
+        <f t="shared" ref="J59:J77" si="14">IF($F59="разово",IF($L59=12,0,$I59),IF($F59="мес",$D59*$E59*(($G59&lt;=1)+($G59&lt;=2)),IF($F59="год",$D59*$E59/12*(($G59&lt;=1)+($G59&lt;=2)),$I59/2)))</f>
         <v>4869152.0999999996</v>
       </c>
       <c r="K59" s="5">
-        <f>IF($F59="разово",IF($L59=12,$I59,0),IF($F59="мес",$D59*$E59*($G59&lt;=3),IF($F59="год",$D59*$E59/12*($G59&lt;=3),$I59/2)))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L59" s="89">
@@ -10876,18 +10895,18 @@
         <v>2</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="I60" s="5">
+        <f t="shared" si="13"/>
+        <v>200000</v>
+      </c>
+      <c r="J60" s="5">
+        <f t="shared" si="14"/>
+        <v>100000</v>
+      </c>
+      <c r="K60" s="5">
         <f t="shared" si="9"/>
-        <v>200000</v>
-      </c>
-      <c r="J60" s="5">
-        <f>IF($F60="разово",IF($L60=12,0,$I60),IF($F60="мес",$D60*$E60*(($G60&lt;=1)+($G60&lt;=2)),IF($F60="год",$D60*$E60/12*(($G60&lt;=1)+($G60&lt;=2)),$I60/2)))</f>
-        <v>100000</v>
-      </c>
-      <c r="K60" s="5">
-        <f>IF($F60="разово",IF($L60=12,$I60,0),IF($F60="мес",$D60*$E60*($G60&lt;=3),IF($F60="год",$D60*$E60/12*($G60&lt;=3),$I60/2)))</f>
         <v>100000</v>
       </c>
       <c r="L60" s="89"/>
@@ -10916,15 +10935,15 @@
       </c>
       <c r="H61" s="4"/>
       <c r="I61" s="5">
+        <f t="shared" si="13"/>
+        <v>60000</v>
+      </c>
+      <c r="J61" s="5">
+        <f t="shared" si="14"/>
+        <v>30000</v>
+      </c>
+      <c r="K61" s="5">
         <f t="shared" si="9"/>
-        <v>60000</v>
-      </c>
-      <c r="J61" s="5">
-        <f>IF($F61="разово",IF($L61=12,0,$I61),IF($F61="мес",$D61*$E61*(($G61&lt;=1)+($G61&lt;=2)),IF($F61="год",$D61*$E61/12*(($G61&lt;=1)+($G61&lt;=2)),$I61/2)))</f>
-        <v>30000</v>
-      </c>
-      <c r="K61" s="5">
-        <f>IF($F61="разово",IF($L61=12,$I61,0),IF($F61="мес",$D61*$E61*($G61&lt;=3),IF($F61="год",$D61*$E61/12*($G61&lt;=3),$I61/2)))</f>
         <v>30000</v>
       </c>
       <c r="L61" s="89"/>
@@ -10953,15 +10972,15 @@
       </c>
       <c r="H62" s="4"/>
       <c r="I62" s="5">
+        <f t="shared" si="13"/>
+        <v>100000</v>
+      </c>
+      <c r="J62" s="5">
+        <f t="shared" si="14"/>
+        <v>50000</v>
+      </c>
+      <c r="K62" s="5">
         <f t="shared" si="9"/>
-        <v>100000</v>
-      </c>
-      <c r="J62" s="5">
-        <f>IF($F62="разово",IF($L62=12,0,$I62),IF($F62="мес",$D62*$E62*(($G62&lt;=1)+($G62&lt;=2)),IF($F62="год",$D62*$E62/12*(($G62&lt;=1)+($G62&lt;=2)),$I62/2)))</f>
-        <v>50000</v>
-      </c>
-      <c r="K62" s="5">
-        <f>IF($F62="разово",IF($L62=12,$I62,0),IF($F62="мес",$D62*$E62*($G62&lt;=3),IF($F62="год",$D62*$E62/12*($G62&lt;=3),$I62/2)))</f>
         <v>50000</v>
       </c>
       <c r="L62" s="89"/>
@@ -10971,10 +10990,10 @@
         <v>111</v>
       </c>
       <c r="B63" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="C63" s="105" t="s">
         <v>560</v>
-      </c>
-      <c r="C63" s="105" t="s">
-        <v>561</v>
       </c>
       <c r="D63" s="9">
         <v>2</v>
@@ -10990,18 +11009,18 @@
         <v>2</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="I63" s="5">
         <f>IF(F63="разово",IF(G63&lt;=3,D63*E63,0),IF(F63="мес",D63*E63*MAX(0,4-G63),D63*E63*MAX(0,4-G63)/12))</f>
         <v>18932</v>
       </c>
       <c r="J63" s="5">
-        <f>IF($F63="разово",IF($L63=12,0,$I63),IF($F63="мес",$D63*$E63*(($G63&lt;=1)+($G63&lt;=2)),IF($F63="год",$D63*$E63/12*(($G63&lt;=1)+($G63&lt;=2)),$I63/2)))</f>
+        <f t="shared" si="14"/>
         <v>9466</v>
       </c>
       <c r="K63" s="5">
-        <f>IF($F63="разово",IF($L63=12,$I63,0),IF($F63="мес",$D63*$E63*($G63&lt;=3),IF($F63="год",$D63*$E63/12*($G63&lt;=3),$I63/2)))</f>
+        <f t="shared" si="9"/>
         <v>9466</v>
       </c>
       <c r="L63" s="89"/>
@@ -11030,15 +11049,15 @@
       </c>
       <c r="H64" s="4"/>
       <c r="I64" s="5">
+        <f t="shared" si="13"/>
+        <v>60000</v>
+      </c>
+      <c r="J64" s="5">
+        <f t="shared" si="14"/>
+        <v>30000</v>
+      </c>
+      <c r="K64" s="5">
         <f t="shared" si="9"/>
-        <v>60000</v>
-      </c>
-      <c r="J64" s="5">
-        <f>IF($F64="разово",IF($L64=12,0,$I64),IF($F64="мес",$D64*$E64*(($G64&lt;=1)+($G64&lt;=2)),IF($F64="год",$D64*$E64/12*(($G64&lt;=1)+($G64&lt;=2)),$I64/2)))</f>
-        <v>30000</v>
-      </c>
-      <c r="K64" s="5">
-        <f>IF($F64="разово",IF($L64=12,$I64,0),IF($F64="мес",$D64*$E64*($G64&lt;=3),IF($F64="год",$D64*$E64/12*($G64&lt;=3),$I64/2)))</f>
         <v>30000</v>
       </c>
       <c r="L64" s="89"/>
@@ -11048,7 +11067,7 @@
         <v>111</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C65" t="s">
         <v>113</v>
@@ -11067,18 +11086,18 @@
         <v>2</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I65" s="5">
+        <f t="shared" si="13"/>
+        <v>48250</v>
+      </c>
+      <c r="J65" s="5">
+        <f t="shared" si="14"/>
+        <v>24125</v>
+      </c>
+      <c r="K65" s="5">
         <f t="shared" si="9"/>
-        <v>48250</v>
-      </c>
-      <c r="J65" s="5">
-        <f>IF($F65="разово",IF($L65=12,0,$I65),IF($F65="мес",$D65*$E65*(($G65&lt;=1)+($G65&lt;=2)),IF($F65="год",$D65*$E65/12*(($G65&lt;=1)+($G65&lt;=2)),$I65/2)))</f>
-        <v>24125</v>
-      </c>
-      <c r="K65" s="5">
-        <f>IF($F65="разово",IF($L65=12,$I65,0),IF($F65="мес",$D65*$E65*($G65&lt;=3),IF($F65="год",$D65*$E65/12*($G65&lt;=3),$I65/2)))</f>
         <v>24125</v>
       </c>
       <c r="L65" s="89"/>
@@ -11088,7 +11107,7 @@
         <v>111</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C66" t="s">
         <v>103</v>
@@ -11107,18 +11126,18 @@
         <v>1</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I66" s="5">
-        <f t="shared" ref="I66" si="10">IF(F66="разово",IF(G66&lt;=3,D66*E66,0),IF(F66="мес",D66*E66*MAX(0,4-G66),D66*E66*MAX(0,4-G66)/12))</f>
+        <f t="shared" ref="I66" si="15">IF(F66="разово",IF(G66&lt;=3,D66*E66,0),IF(F66="мес",D66*E66*MAX(0,4-G66),D66*E66*MAX(0,4-G66)/12))</f>
         <v>20048</v>
       </c>
       <c r="J66" s="5">
-        <f>IF($F66="разово",IF($L66=12,0,$I66),IF($F66="мес",$D66*$E66*(($G66&lt;=1)+($G66&lt;=2)),IF($F66="год",$D66*$E66/12*(($G66&lt;=1)+($G66&lt;=2)),$I66/2)))</f>
+        <f t="shared" si="14"/>
         <v>20048</v>
       </c>
       <c r="K66" s="5">
-        <f>IF($F66="разово",IF($L66=12,$I66,0),IF($F66="мес",$D66*$E66*($G66&lt;=3),IF($F66="год",$D66*$E66/12*($G66&lt;=3),$I66/2)))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L66" s="89">
@@ -11149,15 +11168,15 @@
       </c>
       <c r="H67" s="4"/>
       <c r="I67" s="5">
+        <f t="shared" si="13"/>
+        <v>200000</v>
+      </c>
+      <c r="J67" s="5">
+        <f t="shared" si="14"/>
+        <v>100000</v>
+      </c>
+      <c r="K67" s="5">
         <f t="shared" si="9"/>
-        <v>200000</v>
-      </c>
-      <c r="J67" s="5">
-        <f>IF($F67="разово",IF($L67=12,0,$I67),IF($F67="мес",$D67*$E67*(($G67&lt;=1)+($G67&lt;=2)),IF($F67="год",$D67*$E67/12*(($G67&lt;=1)+($G67&lt;=2)),$I67/2)))</f>
-        <v>100000</v>
-      </c>
-      <c r="K67" s="5">
-        <f>IF($F67="разово",IF($L67=12,$I67,0),IF($F67="мес",$D67*$E67*($G67&lt;=3),IF($F67="год",$D67*$E67/12*($G67&lt;=3),$I67/2)))</f>
         <v>100000</v>
       </c>
       <c r="L67" s="89"/>
@@ -11185,18 +11204,18 @@
         <v>2</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="I68" s="5">
+        <f t="shared" si="13"/>
+        <v>266000</v>
+      </c>
+      <c r="J68" s="5">
+        <f t="shared" si="14"/>
+        <v>133000</v>
+      </c>
+      <c r="K68" s="5">
         <f t="shared" si="9"/>
-        <v>266000</v>
-      </c>
-      <c r="J68" s="5">
-        <f>IF($F68="разово",IF($L68=12,0,$I68),IF($F68="мес",$D68*$E68*(($G68&lt;=1)+($G68&lt;=2)),IF($F68="год",$D68*$E68/12*(($G68&lt;=1)+($G68&lt;=2)),$I68/2)))</f>
-        <v>133000</v>
-      </c>
-      <c r="K68" s="5">
-        <f>IF($F68="разово",IF($L68=12,$I68,0),IF($F68="мес",$D68*$E68*($G68&lt;=3),IF($F68="год",$D68*$E68/12*($G68&lt;=3),$I68/2)))</f>
         <v>133000</v>
       </c>
       <c r="L68" s="89"/>
@@ -11225,15 +11244,15 @@
       </c>
       <c r="H69" s="4"/>
       <c r="I69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>45000</v>
       </c>
       <c r="J69" s="5">
-        <f>IF($F69="разово",IF($L69=12,0,$I69),IF($F69="мес",$D69*$E69*(($G69&lt;=1)+($G69&lt;=2)),IF($F69="год",$D69*$E69/12*(($G69&lt;=1)+($G69&lt;=2)),$I69/2)))</f>
+        <f t="shared" si="14"/>
         <v>22500</v>
       </c>
       <c r="K69" s="5">
-        <f>IF($F69="разово",IF($L69=12,$I69,0),IF($F69="мес",$D69*$E69*($G69&lt;=3),IF($F69="год",$D69*$E69/12*($G69&lt;=3),$I69/2)))</f>
+        <f t="shared" ref="K69:K77" si="16">IF($F69="разово",IF($L69=12,$I69,0),IF($F69="мес",$D69*$E69*($G69&lt;=3),IF($F69="год",$D69*$E69/12*($G69&lt;=3),$I69/2)))</f>
         <v>22500</v>
       </c>
       <c r="L69" s="89"/>
@@ -11264,15 +11283,15 @@
         <v>127</v>
       </c>
       <c r="I70" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>120000</v>
       </c>
       <c r="J70" s="5">
-        <f>IF($F70="разово",IF($L70=12,0,$I70),IF($F70="мес",$D70*$E70*(($G70&lt;=1)+($G70&lt;=2)),IF($F70="год",$D70*$E70/12*(($G70&lt;=1)+($G70&lt;=2)),$I70/2)))</f>
+        <f t="shared" si="14"/>
         <v>60000</v>
       </c>
       <c r="K70" s="5">
-        <f>IF($F70="разово",IF($L70=12,$I70,0),IF($F70="мес",$D70*$E70*($G70&lt;=3),IF($F70="год",$D70*$E70/12*($G70&lt;=3),$I70/2)))</f>
+        <f t="shared" si="16"/>
         <v>60000</v>
       </c>
       <c r="L70" s="89"/>
@@ -11282,7 +11301,7 @@
         <v>121</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C71" t="s">
         <v>126</v>
@@ -11301,18 +11320,18 @@
         <v>2</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="I71" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>79447</v>
       </c>
       <c r="J71" s="5">
-        <f>IF($F71="разово",IF($L71=12,0,$I71),IF($F71="мес",$D71*$E71*(($G71&lt;=1)+($G71&lt;=2)),IF($F71="год",$D71*$E71/12*(($G71&lt;=1)+($G71&lt;=2)),$I71/2)))</f>
+        <f t="shared" si="14"/>
         <v>79447</v>
       </c>
       <c r="K71" s="5">
-        <f>IF($F71="разово",IF($L71=12,$I71,0),IF($F71="мес",$D71*$E71*($G71&lt;=3),IF($F71="год",$D71*$E71/12*($G71&lt;=3),$I71/2)))</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L71" s="89">
@@ -11324,10 +11343,10 @@
         <v>121</v>
       </c>
       <c r="B72" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="C72" s="102" t="s">
         <v>517</v>
-      </c>
-      <c r="C72" s="102" t="s">
-        <v>518</v>
       </c>
       <c r="D72" s="9">
         <v>1</v>
@@ -11342,18 +11361,18 @@
         <v>2</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="I72" s="5">
         <f>IF(F72="разово",IF(G72&lt;=3,D72*E72,0),IF(F72="мес",D72*E72*MAX(0,4-G72),D72*E72*MAX(0,4-G72)/12))</f>
         <v>76000</v>
       </c>
       <c r="J72" s="5">
-        <f>IF($F72="разово",IF($L72=12,0,$I72),IF($F72="мес",$D72*$E72*(($G72&lt;=1)+($G72&lt;=2)),IF($F72="год",$D72*$E72/12*(($G72&lt;=1)+($G72&lt;=2)),$I72/2)))</f>
+        <f t="shared" si="14"/>
         <v>38000</v>
       </c>
       <c r="K72" s="5">
-        <f>IF($F72="разово",IF($L72=12,$I72,0),IF($F72="мес",$D72*$E72*($G72&lt;=3),IF($F72="год",$D72*$E72/12*($G72&lt;=3),$I72/2)))</f>
+        <f t="shared" si="16"/>
         <v>38000</v>
       </c>
       <c r="L72" s="89"/>
@@ -11379,11 +11398,11 @@
         <v>2000000</v>
       </c>
       <c r="J73" s="5">
-        <f>IF($F73="разово",IF($L73=12,0,$I73),IF($F73="мес",$D73*$E73*(($G73&lt;=1)+($G73&lt;=2)),IF($F73="год",$D73*$E73/12*(($G73&lt;=1)+($G73&lt;=2)),$I73/2)))</f>
+        <f t="shared" si="14"/>
         <v>1000000</v>
       </c>
       <c r="K73" s="5">
-        <f>IF($F73="разово",IF($L73=12,$I73,0),IF($F73="мес",$D73*$E73*($G73&lt;=3),IF($F73="год",$D73*$E73/12*($G73&lt;=3),$I73/2)))</f>
+        <f t="shared" si="16"/>
         <v>1000000</v>
       </c>
       <c r="L73" s="89"/>
@@ -11412,15 +11431,15 @@
       </c>
       <c r="H74" s="4"/>
       <c r="I74" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>300000</v>
       </c>
       <c r="J74" s="5">
-        <f>IF($F74="разово",IF($L74=12,0,$I74),IF($F74="мес",$D74*$E74*(($G74&lt;=1)+($G74&lt;=2)),IF($F74="год",$D74*$E74/12*(($G74&lt;=1)+($G74&lt;=2)),$I74/2)))</f>
+        <f t="shared" si="14"/>
         <v>150000</v>
       </c>
       <c r="K74" s="5">
-        <f>IF($F74="разово",IF($L74=12,$I74,0),IF($F74="мес",$D74*$E74*($G74&lt;=3),IF($F74="год",$D74*$E74/12*($G74&lt;=3),$I74/2)))</f>
+        <f t="shared" si="16"/>
         <v>150000</v>
       </c>
       <c r="L74" s="89"/>
@@ -11449,15 +11468,15 @@
       </c>
       <c r="H75" s="4"/>
       <c r="I75" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>50000</v>
       </c>
       <c r="J75" s="5">
-        <f>IF($F75="разово",IF($L75=12,0,$I75),IF($F75="мес",$D75*$E75*(($G75&lt;=1)+($G75&lt;=2)),IF($F75="год",$D75*$E75/12*(($G75&lt;=1)+($G75&lt;=2)),$I75/2)))</f>
+        <f t="shared" si="14"/>
         <v>25000</v>
       </c>
       <c r="K75" s="5">
-        <f>IF($F75="разово",IF($L75=12,$I75,0),IF($F75="мес",$D75*$E75*($G75&lt;=3),IF($F75="год",$D75*$E75/12*($G75&lt;=3),$I75/2)))</f>
+        <f t="shared" si="16"/>
         <v>25000</v>
       </c>
       <c r="L75" s="89"/>
@@ -11467,7 +11486,7 @@
         <v>132</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C76" t="s">
         <v>103</v>
@@ -11485,18 +11504,18 @@
         <v>1</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I76" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>350000</v>
       </c>
       <c r="J76" s="5">
-        <f>IF($F76="разово",IF($L76=12,0,$I76),IF($F76="мес",$D76*$E76*(($G76&lt;=1)+($G76&lt;=2)),IF($F76="год",$D76*$E76/12*(($G76&lt;=1)+($G76&lt;=2)),$I76/2)))</f>
+        <f t="shared" si="14"/>
         <v>350000</v>
       </c>
       <c r="K76" s="5">
-        <f>IF($F76="разово",IF($L76=12,$I76,0),IF($F76="мес",$D76*$E76*($G76&lt;=3),IF($F76="год",$D76*$E76/12*($G76&lt;=3),$I76/2)))</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L76" s="89">
@@ -11508,7 +11527,7 @@
         <v>132</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C77" t="s">
         <v>130</v>
@@ -11525,15 +11544,15 @@
       </c>
       <c r="H77" s="4"/>
       <c r="I77" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J77" s="5">
-        <f>IF($F77="разово",IF($L77=12,0,$I77),IF($F77="мес",$D77*$E77*(($G77&lt;=1)+($G77&lt;=2)),IF($F77="год",$D77*$E77/12*(($G77&lt;=1)+($G77&lt;=2)),$I77/2)))</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="K77" s="5">
-        <f>IF($F77="разово",IF($L77=12,$I77,0),IF($F77="мес",$D77*$E77*($G77&lt;=3),IF($F77="год",$D77*$E77/12*($G77&lt;=3),$I77/2)))</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L77" s="89"/>
@@ -11593,10 +11612,10 @@
         <v>90</v>
       </c>
       <c r="H4" s="34" t="s">
+        <v>562</v>
+      </c>
+      <c r="I4" s="34" t="s">
         <v>563</v>
-      </c>
-      <c r="I4" s="34" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -11604,7 +11623,7 @@
         <v>273</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C5" t="s">
         <v>234</v>
@@ -11632,7 +11651,7 @@
         <v>273</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C6" t="s">
         <v>234</v>
@@ -11675,7 +11694,7 @@
         <v>17284000</v>
       </c>
       <c r="H7" s="5">
-        <f t="shared" ref="H7:J8" si="0">$G7*1/3</f>
+        <f t="shared" ref="H7:I8" si="0">$G7*1/3</f>
         <v>5761333.333333333</v>
       </c>
       <c r="I7" s="5">
@@ -11688,7 +11707,7 @@
         <v>273</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C8" t="s">
         <v>234</v>
@@ -11716,7 +11735,7 @@
         <v>273</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C9" t="s">
         <v>234</v>
@@ -11744,7 +11763,7 @@
         <v>273</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C10" t="s">
         <v>234</v>
@@ -11825,45 +11844,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="107" t="s">
-        <v>395</v>
-      </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
+      <c r="A1" s="108" t="s">
+        <v>394</v>
+      </c>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>395</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>396</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>397</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>398</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>399</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -11875,13 +11894,13 @@
     </row>
     <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
+        <v>401</v>
+      </c>
+      <c r="B5" s="54" t="s">
         <v>402</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="C5" s="55" t="s">
         <v>403</v>
-      </c>
-      <c r="C5" s="55" t="s">
-        <v>404</v>
       </c>
       <c r="D5" s="55">
         <v>56</v>
@@ -11896,13 +11915,13 @@
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
+        <v>404</v>
+      </c>
+      <c r="B6" s="57" t="s">
         <v>405</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="C6" s="55" t="s">
         <v>406</v>
-      </c>
-      <c r="C6" s="55" t="s">
-        <v>407</v>
       </c>
       <c r="D6" s="55">
         <v>56</v>
@@ -11918,13 +11937,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
+        <v>407</v>
+      </c>
+      <c r="B7" s="57" t="s">
         <v>408</v>
       </c>
-      <c r="B7" s="57" t="s">
-        <v>409</v>
-      </c>
       <c r="C7" s="55" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D7" s="55">
         <v>6</v>
@@ -11939,13 +11958,13 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
+        <v>409</v>
+      </c>
+      <c r="B8" s="57" t="s">
         <v>410</v>
       </c>
-      <c r="B8" s="57" t="s">
-        <v>411</v>
-      </c>
       <c r="C8" s="55" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D8" s="55">
         <v>6</v>
@@ -11960,13 +11979,13 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
+        <v>411</v>
+      </c>
+      <c r="B9" s="57" t="s">
         <v>412</v>
       </c>
-      <c r="B9" s="57" t="s">
-        <v>413</v>
-      </c>
       <c r="C9" s="55" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D9" s="55">
         <v>6</v>
@@ -11981,13 +12000,13 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
+        <v>413</v>
+      </c>
+      <c r="B10" s="57" t="s">
         <v>414</v>
       </c>
-      <c r="B10" s="57" t="s">
-        <v>415</v>
-      </c>
       <c r="C10" s="55" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D10" s="55">
         <v>48</v>
@@ -12003,7 +12022,7 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51"/>
       <c r="B11" s="59" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C11" s="49"/>
       <c r="D11" s="55"/>
@@ -12016,7 +12035,7 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51"/>
       <c r="B12" s="60" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C12" s="61"/>
       <c r="D12" s="61"/>

--- a/TAZA/_документы/Бюджет ТАЗА – 2 месяца (ноябрь–декабрь).xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА – 2 месяца (ноябрь–декабрь).xlsx
@@ -1379,9 +1379,6 @@
     <t xml:space="preserve">  в т.ч. проектный офис «Таза Қазақстан», чел.</t>
   </si>
   <si>
-    <t>1. Персонал: оклады и отчисления работодателя (СН, ОПВР, СО, ООСМС)</t>
-  </si>
-  <si>
     <t>4. Командировки по РК</t>
   </si>
   <si>
@@ -2120,10 +2117,13 @@
     <t>Итого ноябрь–декабрь 2026</t>
   </si>
   <si>
-    <t>В. Долг по зарплате и налогам за июль–октябрь 2026 (4 действующих работника Фонда: оклады и отчисления работодателя за 4 месяца, выплата в ноябре)</t>
-  </si>
-  <si>
-    <t>ВСЕГО (А + Б + В)</t>
+    <t>В. Долг по зарплате и налогам за июль–октябрь 2026</t>
+  </si>
+  <si>
+    <t>1. Оплата труда и отчисления работодателя</t>
+  </si>
+  <si>
+    <t>ВСЕГО (А + Б)</t>
   </si>
 </sst>
 </file>
@@ -2846,7 +2846,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -2854,13 +2854,13 @@
         <v>0</v>
       </c>
       <c r="B3" s="35" t="s">
+        <v>561</v>
+      </c>
+      <c r="C3" s="35" t="s">
         <v>562</v>
       </c>
-      <c r="C3" s="35" t="s">
-        <v>563</v>
-      </c>
       <c r="D3" s="35" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2893,24 +2893,24 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>332</v>
+        <v>571</v>
       </c>
       <c r="B6" s="38">
-        <f>SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36*(Штат!$I$5:$I$36&lt;=2))</f>
-        <v>25551690</v>
+        <f>(SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36*(Штат!$I$5:$I$36&lt;=2)))+B7+B20</f>
+        <v>63001690</v>
       </c>
       <c r="C6" s="38">
-        <f>SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36*(Штат!$I$5:$I$36&lt;=3))</f>
-        <v>27034580</v>
+        <f>(SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36*(Штат!$I$5:$I$36&lt;=3)))+C7+C20</f>
+        <v>36424100</v>
       </c>
       <c r="D6" s="40">
-        <f t="shared" ref="D6:D21" si="0">B6+C6</f>
-        <v>52586270</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <f t="shared" ref="D6:D19" si="0">B6+C6</f>
+        <v>99425790</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B7" s="38">
         <v>0</v>
@@ -2926,7 +2926,7 @@
     </row>
     <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B8" s="38">
         <f>SUMPRODUCT(Аутсорс!$I$4:$I$10*((Аутсорс!$J$4:$J$10&lt;=1)+(Аутсорс!$J$4:$J$10&lt;=2)))</f>
@@ -2943,7 +2943,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B9" s="38">
         <f>Штат!$N$37</f>
@@ -2959,7 +2959,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="36" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B10" s="38">
         <f>Командировки!$G$12/2</f>
@@ -2976,7 +2976,7 @@
     </row>
     <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B11" s="38">
         <f>SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Оснащение")</f>
@@ -2993,7 +2993,7 @@
     </row>
     <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B12" s="38">
         <f>SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Офис")</f>
@@ -3010,7 +3010,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="36" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B13" s="38">
         <f>SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Цифровые")</f>
@@ -3027,7 +3027,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="36" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B14" s="38">
         <f>SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Медиа")</f>
@@ -3044,31 +3044,31 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="39" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B15" s="40">
-        <f>SUM(B6:B14)</f>
-        <v>60618022.855529949</v>
+        <f>SUM(B6:B14)-B7</f>
+        <v>98068022.855529949</v>
       </c>
       <c r="C15" s="40">
-        <f>SUM(C6:C14)</f>
+        <f>SUM(C6:C14)-C7</f>
         <v>53542054.350000001</v>
       </c>
       <c r="D15" s="40">
         <f t="shared" si="0"/>
-        <v>114160077.20552996</v>
+        <v>151610077.20552996</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B16" s="38">
-        <f>B15*Резерв+SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Прочие")</f>
+        <f>(B15-B20)*Резерв+SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Прочие")</f>
         <v>6411802.2855529953</v>
       </c>
       <c r="C16" s="38">
-        <f>C15*Резерв+SUMIFS('Оснащение и офис'!$K$5:$K$77,'Оснащение и офис'!$A$5:$A$77,"Прочие")</f>
+        <f>(C15-C20)*Резерв+SUMIFS('Оснащение и офис'!$K$5:$K$77,'Оснащение и офис'!$A$5:$A$77,"Прочие")</f>
         <v>5354205.4350000005</v>
       </c>
       <c r="D16" s="40">
@@ -3078,7 +3078,7 @@
     </row>
     <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="36" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B17" s="38">
         <f>((B11+B12+B13+B14)-'Оснащение и офис'!$J$59)*(1+Резерв)*НДС</f>
@@ -3095,11 +3095,11 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B18" s="42">
         <f>B15+B16+B17</f>
-        <v>70691493.815199077</v>
+        <v>108141493.81519908</v>
       </c>
       <c r="C18" s="42">
         <f>C15+C16+C17</f>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="D18" s="42">
         <f t="shared" si="0"/>
-        <v>131055039.56979908</v>
+        <v>168505039.56979907</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="39" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B19" s="40">
         <f>Проекты!$H$13</f>
@@ -3127,20 +3127,19 @@
         <v>70077146.666666672</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="39" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B20" s="40">
-        <f>4*SUMPRODUCT((Штат!$F$5:$F$36="действующий")*(Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36)</f>
-        <v>26408960</v>
+        <v>37450000</v>
       </c>
       <c r="C20" s="40">
         <v>0</v>
       </c>
       <c r="D20" s="40">
         <f>SUM(B20:C20)</f>
-        <v>26408960</v>
+        <v>37450000</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -3148,35 +3147,35 @@
         <v>572</v>
       </c>
       <c r="B21" s="44">
-        <f>B18+B19+B20</f>
-        <v>135346427.14853242</v>
+        <f>B18+B19</f>
+        <v>146387467.14853242</v>
       </c>
       <c r="C21" s="44">
-        <f>C18+C19+C20</f>
+        <f>C18+C19</f>
         <v>92194719.087933332</v>
       </c>
       <c r="D21" s="44">
-        <f>D18+D19+D20</f>
-        <v>227541146.23646575</v>
+        <f>D18+D19</f>
+        <v>238582186.23646575</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="106" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B23" s="44">
         <f>B21</f>
-        <v>135346427.14853242</v>
+        <v>146387467.14853242</v>
       </c>
       <c r="C23" s="44">
         <f>B23+C21</f>
-        <v>227541146.23646575</v>
+        <v>238582186.23646575</v>
       </c>
       <c r="D23" s="44"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="106" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B24" s="44"/>
       <c r="C24" s="44"/>
@@ -3186,19 +3185,19 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="43" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B25" s="44">
         <f>$D$24-B23</f>
-        <v>114653572.85146758</v>
+        <v>103612532.85146758</v>
       </c>
       <c r="C25" s="44">
         <f>$D$24-C23</f>
-        <v>22458853.763534248</v>
+        <v>11417813.763534248</v>
       </c>
       <c r="D25" s="44">
         <f>D24-D21</f>
-        <v>22458853.763534248</v>
+        <v>11417813.763534248</v>
       </c>
     </row>
   </sheetData>
@@ -3225,7 +3224,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="108" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B1" s="108"/>
       <c r="C1" s="108"/>
@@ -3244,25 +3243,25 @@
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>394</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>395</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>396</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>397</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>398</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3274,13 +3273,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B5" s="57" t="s">
+        <v>417</v>
+      </c>
+      <c r="C5" s="55" t="s">
         <v>418</v>
-      </c>
-      <c r="C5" s="55" t="s">
-        <v>419</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -3295,13 +3294,13 @@
     </row>
     <row r="6" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -3317,13 +3316,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -3338,13 +3337,13 @@
     </row>
     <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B8" s="57" t="s">
+        <v>421</v>
+      </c>
+      <c r="C8" s="55" t="s">
         <v>422</v>
-      </c>
-      <c r="C8" s="55" t="s">
-        <v>423</v>
       </c>
       <c r="D8" s="55">
         <v>1</v>
@@ -3359,13 +3358,13 @@
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B9" s="57" t="s">
+        <v>423</v>
+      </c>
+      <c r="C9" s="55" t="s">
         <v>424</v>
-      </c>
-      <c r="C9" s="55" t="s">
-        <v>425</v>
       </c>
       <c r="D9" s="74">
         <v>100</v>
@@ -3380,13 +3379,13 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D10" s="74">
         <v>100</v>
@@ -3402,10 +3401,10 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51"/>
       <c r="B11" s="57" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D11" s="74">
         <v>1</v>
@@ -3420,13 +3419,13 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D12" s="55">
         <v>4</v>
@@ -3441,13 +3440,13 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="51" t="s">
+        <v>427</v>
+      </c>
+      <c r="B13" s="75" t="s">
         <v>428</v>
       </c>
-      <c r="B13" s="75" t="s">
-        <v>429</v>
-      </c>
       <c r="C13" s="76" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D13" s="76">
         <v>1</v>
@@ -3463,7 +3462,7 @@
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="51"/>
       <c r="B14" s="59" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C14" s="49"/>
       <c r="D14" s="55"/>
@@ -3476,7 +3475,7 @@
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="51"/>
       <c r="B15" s="60" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C15" s="61"/>
       <c r="D15" s="61"/>
@@ -3533,7 +3532,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="108" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B1" s="108"/>
       <c r="C1" s="108"/>
@@ -3552,25 +3551,25 @@
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>394</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>395</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>396</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>397</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>398</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3582,13 +3581,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B5" s="57" t="s">
+        <v>430</v>
+      </c>
+      <c r="C5" s="55" t="s">
         <v>431</v>
-      </c>
-      <c r="C5" s="55" t="s">
-        <v>432</v>
       </c>
       <c r="D5" s="55">
         <v>4</v>
@@ -3603,13 +3602,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B6" s="57" t="s">
+        <v>432</v>
+      </c>
+      <c r="C6" s="55" t="s">
         <v>433</v>
-      </c>
-      <c r="C6" s="55" t="s">
-        <v>434</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -3625,13 +3624,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -3647,7 +3646,7 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51"/>
       <c r="B8" s="59" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C8" s="49"/>
       <c r="D8" s="55"/>
@@ -3660,7 +3659,7 @@
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="51"/>
       <c r="B9" s="60" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C9" s="61"/>
       <c r="D9" s="61"/>
@@ -3717,7 +3716,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="108" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B1" s="108"/>
       <c r="C1" s="108"/>
@@ -3736,25 +3735,25 @@
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>394</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>395</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>396</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>397</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>398</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3766,13 +3765,13 @@
     </row>
     <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D5" s="55">
         <v>6</v>
@@ -3787,13 +3786,13 @@
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -3809,13 +3808,13 @@
     </row>
     <row r="7" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -3830,13 +3829,13 @@
     </row>
     <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D8" s="55">
         <v>9</v>
@@ -3851,13 +3850,13 @@
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D9" s="74">
         <v>32</v>
@@ -3872,13 +3871,13 @@
     </row>
     <row r="10" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D10" s="55">
         <v>3</v>
@@ -3893,13 +3892,13 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D11" s="55">
         <v>3</v>
@@ -3916,7 +3915,7 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51"/>
       <c r="B12" s="59" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C12" s="49"/>
       <c r="D12" s="55"/>
@@ -3929,7 +3928,7 @@
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="51"/>
       <c r="B13" s="60" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C13" s="61"/>
       <c r="D13" s="61"/>
@@ -3983,7 +3982,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="108" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B1" s="108"/>
       <c r="C1" s="108"/>
@@ -4002,25 +4001,25 @@
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>394</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>395</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>396</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>397</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>398</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -4032,13 +4031,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -4053,13 +4052,13 @@
     </row>
     <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -4076,7 +4075,7 @@
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51"/>
       <c r="B7" s="59" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C7" s="49"/>
       <c r="D7" s="55"/>
@@ -4089,7 +4088,7 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51"/>
       <c r="B8" s="60" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C8" s="61"/>
       <c r="D8" s="61"/>
@@ -4146,7 +4145,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="108" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B1" s="108"/>
       <c r="C1" s="108"/>
@@ -4165,25 +4164,25 @@
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>394</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>395</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>396</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>397</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>398</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -4195,13 +4194,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -4217,7 +4216,7 @@
     <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="51"/>
       <c r="B6" s="59" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C6" s="49"/>
       <c r="D6" s="55"/>
@@ -4231,7 +4230,7 @@
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51"/>
       <c r="B7" s="60" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C7" s="61"/>
       <c r="D7" s="61"/>
@@ -4289,7 +4288,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -4472,7 +4471,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -4623,7 +4622,7 @@
         <v>188</v>
       </c>
       <c r="B20" s="104" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C20" s="104" t="s">
         <v>103</v>
@@ -4640,13 +4639,13 @@
         <v>4548</v>
       </c>
       <c r="G20" s="104" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="32"/>
@@ -4912,7 +4911,7 @@
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -5203,14 +5202,14 @@
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B15" s="8">
         <f>ROUND(0.29%*12*SUMIFS(Штат!$H$5:$H$36,Штат!$E$5:$E$36,"штат",Штат!$F$5:$F$36,"новая"),-3)</f>
         <v>713000</v>
       </c>
       <c r="C15" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5495,7 +5494,7 @@
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -5569,7 +5568,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -5639,13 +5638,13 @@
         <v>74</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>76</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>77</v>
@@ -5654,7 +5653,7 @@
         <v>316</v>
       </c>
       <c r="Q4" s="88" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -5710,7 +5709,7 @@
         <v>3636460</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Q5" s="89"/>
     </row>
@@ -5722,7 +5721,7 @@
         <v>263</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>81</v>
@@ -5767,7 +5766,7 @@
         <v>3189340</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Q6" s="89"/>
     </row>
@@ -5824,7 +5823,7 @@
         <v>3189340</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q7" s="89"/>
     </row>
@@ -5836,7 +5835,7 @@
         <v>207</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>81</v>
@@ -5881,7 +5880,7 @@
         <v>3223292.3809523811</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q8" s="89">
         <v>1</v>
@@ -5898,7 +5897,7 @@
         <v>237</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>79</v>
@@ -5940,7 +5939,7 @@
         <v>1516842.3809523811</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Q9" s="89"/>
     </row>
@@ -5952,7 +5951,7 @@
         <v>236</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D10" s="17" t="s">
         <v>239</v>
@@ -5997,7 +5996,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q10" s="89">
         <v>1</v>
@@ -6011,7 +6010,7 @@
         <v>236</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D11" s="21" t="s">
         <v>239</v>
@@ -6056,7 +6055,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="21" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q11" s="89"/>
     </row>
@@ -6227,7 +6226,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Q14" s="89">
         <v>1</v>
@@ -6286,7 +6285,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P15" s="17" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q15" s="89">
         <v>1</v>
@@ -6345,7 +6344,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P16" s="17" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Q16" s="89">
         <v>1</v>
@@ -6404,7 +6403,7 @@
         <v>0</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="Q17" s="89"/>
     </row>
@@ -6461,7 +6460,7 @@
         <v>0</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="Q18" s="89"/>
     </row>
@@ -6518,7 +6517,7 @@
         <v>1658372.3809523811</v>
       </c>
       <c r="P19" s="17" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q19" s="89"/>
     </row>
@@ -6533,7 +6532,7 @@
         <v>237</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E20" s="16" t="s">
         <v>79</v>
@@ -6575,7 +6574,7 @@
         <v>2999732.3809523811</v>
       </c>
       <c r="P20" s="17" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q20" s="89">
         <v>1</v>
@@ -6649,7 +6648,7 @@
         <v>247</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>79</v>
@@ -6691,7 +6690,7 @@
         <v>2999732.3809523811</v>
       </c>
       <c r="P22" s="17" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q22" s="89"/>
     </row>
@@ -6748,7 +6747,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q23" s="89">
         <v>1</v>
@@ -6876,7 +6875,7 @@
         <v>246</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>208</v>
@@ -6921,7 +6920,7 @@
         <v>1658372.3809523811</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Q26" s="89">
         <v>1</v>
@@ -6980,7 +6979,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Q27" s="89"/>
     </row>
@@ -7217,13 +7216,13 @@
         <v>35</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E32" s="16" t="s">
         <v>79</v>
@@ -7265,7 +7264,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="17" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q32" s="89"/>
     </row>
@@ -7274,13 +7273,13 @@
         <v>35</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E33" s="16" t="s">
         <v>79</v>
@@ -7322,7 +7321,7 @@
         <v>1881932.3809523811</v>
       </c>
       <c r="P33" s="17" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="Q33" s="89"/>
     </row>
@@ -7331,13 +7330,13 @@
         <v>35</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E34" s="16" t="s">
         <v>79</v>
@@ -7379,7 +7378,7 @@
         <v>1881932.3809523811</v>
       </c>
       <c r="P34" s="17" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q34" s="89"/>
     </row>
@@ -7563,12 +7562,12 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C41" s="7" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H42" s="5">
         <f>SUMPRODUCT(Q5:Q36,H5:H36)</f>
@@ -7577,7 +7576,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H43" s="5">
         <f>H42*(Ставка_ОПВР+Ставка_ООСМС+Ставка_СН*(1-Ставка_ОПВ-Ставка_ВОСМС))</f>
@@ -7586,7 +7585,7 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C44" s="7" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H44" s="6">
         <f>H42+H43</f>
@@ -7595,7 +7594,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -7646,10 +7645,10 @@
         <v>275</v>
       </c>
       <c r="F3" s="103" t="s">
+        <v>518</v>
+      </c>
+      <c r="G3" s="103" t="s">
         <v>519</v>
-      </c>
-      <c r="G3" s="103" t="s">
-        <v>520</v>
       </c>
       <c r="H3" s="25" t="s">
         <v>276</v>
@@ -7672,7 +7671,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>206</v>
@@ -7716,7 +7715,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>206</v>
@@ -7892,13 +7891,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="27" t="s">
+        <v>378</v>
+      </c>
+      <c r="C9" s="27" t="s">
         <v>379</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="D9" s="27" t="s">
         <v>380</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>381</v>
       </c>
       <c r="E9" s="28">
         <v>700000</v>
@@ -8011,7 +8010,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12" s="24" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
   </sheetData>
@@ -8033,12 +8032,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -8049,48 +8048,48 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B4" s="93">
         <v>0.1</v>
       </c>
       <c r="C4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B5" s="94">
         <f>Ставка_ОПВР+Ставка_ООСМС+Ставка_СН*(1-Ставка_ОПВ-Ставка_ВОСМС)</f>
         <v>0.1178</v>
       </c>
       <c r="C5" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="95" t="s">
+        <v>500</v>
+      </c>
+      <c r="B7" s="95" t="s">
         <v>501</v>
       </c>
-      <c r="B7" s="95" t="s">
+      <c r="C7" s="95" t="s">
         <v>502</v>
       </c>
-      <c r="C7" s="95" t="s">
+      <c r="D7" s="95" t="s">
         <v>503</v>
       </c>
-      <c r="D7" s="95" t="s">
+      <c r="E7" s="95" t="s">
         <v>504</v>
       </c>
-      <c r="E7" s="95" t="s">
+      <c r="F7" s="95" t="s">
         <v>505</v>
       </c>
-      <c r="F7" s="95" t="s">
+      <c r="G7" s="95" t="s">
         <v>506</v>
-      </c>
-      <c r="G7" s="95" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -8211,48 +8210,48 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="98" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B14" s="97">
         <f>$B$4*(1+$B$5)</f>
         <v>0.11177999999999999</v>
       </c>
       <c r="C14" s="98" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="98" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B15" s="97">
         <f>$B$4*(1+$B$5)*(1+НДС)</f>
         <v>0.12966479999999997</v>
       </c>
       <c r="C15" s="98" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="99" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B18" s="99"/>
       <c r="C18" s="99"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="98" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B19" s="96">
         <f>Аутсорс!E11</f>
@@ -8262,7 +8261,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="98" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B20" s="96">
         <f>Аутсорс!F11</f>
@@ -8272,7 +8271,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="100" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B21" s="101">
         <f>Аутсорс!F11*2</f>
@@ -8282,7 +8281,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="100" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B22" s="101">
         <f>B21*(1+НДС)</f>
@@ -8292,7 +8291,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="98" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B23" s="96">
         <f>Аутсорс!L11</f>
@@ -8302,7 +8301,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
   </sheetData>
@@ -8351,7 +8350,7 @@
         <v>89</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>90</v>
@@ -8431,7 +8430,7 @@
     </row>
     <row r="8" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C8">
         <f>SUMIFS(Штат!$G$5:$G$36,Штат!$B$5:$B$36,"Департамент социологических*",Штат!$E$5:$E$36,"штат")</f>
@@ -8454,7 +8453,7 @@
     </row>
     <row r="9" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C9">
         <f>SUMIFS(Штат!$G$5:$G$36,Штат!$B$5:$B$36,"Департамент проектного управления*",Штат!$E$5:$E$36,"штат")</f>
@@ -8500,7 +8499,7 @@
     </row>
     <row r="11" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C11">
         <f>SUM(Штат!G22:G29)</f>
@@ -8598,13 +8597,13 @@
         <v>90</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>563</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8630,7 +8629,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I57" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
@@ -8712,7 +8711,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="0"/>
@@ -8735,7 +8734,7 @@
         <v>97</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C8" t="s">
         <v>99</v>
@@ -8754,7 +8753,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="0"/>
@@ -8777,7 +8776,7 @@
         <v>97</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C9" s="80" t="s">
         <v>99</v>
@@ -8796,7 +8795,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" ref="I9" si="3">IF(F9="разово",IF(G9&lt;=3,D9*E9,0),IF(F9="мес",D9*E9*MAX(0,4-G9),D9*E9*MAX(0,4-G9)/12))</f>
@@ -8819,7 +8818,7 @@
         <v>97</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C10" s="81" t="s">
         <v>99</v>
@@ -8838,7 +8837,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" ref="I10" si="4">IF(F10="разово",IF(G10&lt;=3,D10*E10,0),IF(F10="мес",D10*E10*MAX(0,4-G10),D10*E10*MAX(0,4-G10)/12))</f>
@@ -8861,7 +8860,7 @@
         <v>97</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C11" s="82" t="s">
         <v>99</v>
@@ -8880,7 +8879,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" ref="I11" si="5">IF(F11="разово",IF(G11&lt;=3,D11*E11,0),IF(F11="мес",D11*E11*MAX(0,4-G11),D11*E11*MAX(0,4-G11)/12))</f>
@@ -8903,7 +8902,7 @@
         <v>97</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C12" t="s">
         <v>99</v>
@@ -8922,7 +8921,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="0"/>
@@ -8945,7 +8944,7 @@
         <v>97</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C13" s="84" t="s">
         <v>99</v>
@@ -8964,7 +8963,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="I13" s="5">
         <f>IF(F13="разово",IF(G13&lt;=3,D13*E13,0),IF(F13="мес",D13*E13*MAX(0,4-G13),D13*E13*MAX(0,4-G13)/12))</f>
@@ -8987,7 +8986,7 @@
         <v>97</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C14" s="84" t="s">
         <v>99</v>
@@ -9006,7 +9005,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="I14" s="5">
         <f>IF(F14="разово",IF(G14&lt;=3,D14*E14,0),IF(F14="мес",D14*E14*MAX(0,4-G14),D14*E14*MAX(0,4-G14)/12))</f>
@@ -9029,7 +9028,7 @@
         <v>97</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C15" s="83" t="s">
         <v>99</v>
@@ -9048,7 +9047,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" ref="I15" si="6">IF(F15="разово",IF(G15&lt;=3,D15*E15,0),IF(F15="мес",D15*E15*MAX(0,4-G15),D15*E15*MAX(0,4-G15)/12))</f>
@@ -9071,7 +9070,7 @@
         <v>97</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C16" s="92" t="s">
         <v>99</v>
@@ -9090,7 +9089,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" ref="I16:I21" si="7">IF(F16="разово",IF(G16&lt;=3,D16*E16,0),IF(F16="мес",D16*E16*MAX(0,4-G16),D16*E16*MAX(0,4-G16)/12))</f>
@@ -9113,7 +9112,7 @@
         <v>97</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C17" s="87" t="s">
         <v>103</v>
@@ -9132,7 +9131,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="7"/>
@@ -9155,7 +9154,7 @@
         <v>97</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C18" s="91" t="s">
         <v>103</v>
@@ -9174,7 +9173,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="7"/>
@@ -9197,7 +9196,7 @@
         <v>97</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C19" s="85" t="s">
         <v>99</v>
@@ -9216,7 +9215,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="7"/>
@@ -9239,7 +9238,7 @@
         <v>97</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C20" s="86" t="s">
         <v>103</v>
@@ -9258,7 +9257,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="7"/>
@@ -9281,7 +9280,7 @@
         <v>97</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C21" s="86" t="s">
         <v>103</v>
@@ -9300,7 +9299,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="7"/>
@@ -9362,7 +9361,7 @@
         <v>97</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C23" t="s">
         <v>103</v>
@@ -9401,7 +9400,7 @@
         <v>97</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C24" t="s">
         <v>103</v>
@@ -9419,7 +9418,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
@@ -9525,7 +9524,7 @@
         <v>97</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C27" s="86" t="s">
         <v>103</v>
@@ -9544,7 +9543,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I27" s="5">
         <f>IF(F27="разово",IF(G27&lt;=3,D27*E27,0),IF(F27="мес",D27*E27*MAX(0,4-G27),D27*E27*MAX(0,4-G27)/12))</f>
@@ -9949,7 +9948,7 @@
         <v>1</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="0"/>
@@ -9991,7 +9990,7 @@
         <v>1</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="0"/>
@@ -10140,7 +10139,7 @@
         <v>97</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C42" s="105" t="s">
         <v>99</v>
@@ -10159,7 +10158,7 @@
         <v>1</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="I42" s="5">
         <f>IF(F42="разово",IF(G42&lt;=3,D42*E42,0),IF(F42="мес",D42*E42*MAX(0,4-G42),D42*E42*MAX(0,4-G42)/12))</f>
@@ -10224,7 +10223,7 @@
         <v>97</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C44" t="s">
         <v>99</v>
@@ -10243,7 +10242,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="I44" s="5">
         <f t="shared" si="0"/>
@@ -10266,7 +10265,7 @@
         <v>97</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C45" s="90" t="s">
         <v>99</v>
@@ -10285,7 +10284,7 @@
         <v>1</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="I45" s="5">
         <f>IF(F45="разово",IF(G45&lt;=3,D45*E45,0),IF(F45="мес",D45*E45*MAX(0,4-G45),D45*E45*MAX(0,4-G45)/12))</f>
@@ -10308,7 +10307,7 @@
         <v>97</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C46" t="s">
         <v>103</v>
@@ -10326,7 +10325,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="0"/>
@@ -10429,7 +10428,7 @@
         <v>97</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C49" t="s">
         <v>108</v>
@@ -10448,7 +10447,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I49" s="5">
         <f t="shared" si="0"/>
@@ -10552,7 +10551,7 @@
         <v>97</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C52" t="s">
         <v>99</v>
@@ -10571,7 +10570,7 @@
         <v>1</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="I52" s="5">
         <f t="shared" ref="I52:I54" si="12">IF(F52="разово",IF(G52&lt;=3,D52*E52,0),IF(F52="мес",D52*E52*MAX(0,4-G52),D52*E52*MAX(0,4-G52)/12))</f>
@@ -10594,7 +10593,7 @@
         <v>97</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C53" t="s">
         <v>103</v>
@@ -10613,7 +10612,7 @@
         <v>1</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I53" s="5">
         <f t="shared" si="12"/>
@@ -10636,7 +10635,7 @@
         <v>97</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C54" t="s">
         <v>99</v>
@@ -10655,7 +10654,7 @@
         <v>1</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I54" s="5">
         <f t="shared" si="12"/>
@@ -10756,7 +10755,7 @@
         <v>97</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C57" t="s">
         <v>99</v>
@@ -10895,7 +10894,7 @@
         <v>2</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I60" s="5">
         <f t="shared" si="13"/>
@@ -10990,10 +10989,10 @@
         <v>111</v>
       </c>
       <c r="B63" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="C63" s="105" t="s">
         <v>559</v>
-      </c>
-      <c r="C63" s="105" t="s">
-        <v>560</v>
       </c>
       <c r="D63" s="9">
         <v>2</v>
@@ -11009,7 +11008,7 @@
         <v>2</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="I63" s="5">
         <f>IF(F63="разово",IF(G63&lt;=3,D63*E63,0),IF(F63="мес",D63*E63*MAX(0,4-G63),D63*E63*MAX(0,4-G63)/12))</f>
@@ -11067,7 +11066,7 @@
         <v>111</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C65" t="s">
         <v>113</v>
@@ -11086,7 +11085,7 @@
         <v>2</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I65" s="5">
         <f t="shared" si="13"/>
@@ -11107,7 +11106,7 @@
         <v>111</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C66" t="s">
         <v>103</v>
@@ -11126,7 +11125,7 @@
         <v>1</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I66" s="5">
         <f t="shared" ref="I66" si="15">IF(F66="разово",IF(G66&lt;=3,D66*E66,0),IF(F66="мес",D66*E66*MAX(0,4-G66),D66*E66*MAX(0,4-G66)/12))</f>
@@ -11204,7 +11203,7 @@
         <v>2</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I68" s="5">
         <f t="shared" si="13"/>
@@ -11301,7 +11300,7 @@
         <v>121</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C71" t="s">
         <v>126</v>
@@ -11320,7 +11319,7 @@
         <v>2</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="I71" s="5">
         <f t="shared" si="13"/>
@@ -11343,10 +11342,10 @@
         <v>121</v>
       </c>
       <c r="B72" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="C72" s="102" t="s">
         <v>516</v>
-      </c>
-      <c r="C72" s="102" t="s">
-        <v>517</v>
       </c>
       <c r="D72" s="9">
         <v>1</v>
@@ -11361,7 +11360,7 @@
         <v>2</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I72" s="5">
         <f>IF(F72="разово",IF(G72&lt;=3,D72*E72,0),IF(F72="мес",D72*E72*MAX(0,4-G72),D72*E72*MAX(0,4-G72)/12))</f>
@@ -11486,7 +11485,7 @@
         <v>132</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C76" t="s">
         <v>103</v>
@@ -11504,7 +11503,7 @@
         <v>1</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="I76" s="5">
         <f t="shared" si="13"/>
@@ -11527,7 +11526,7 @@
         <v>132</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C77" t="s">
         <v>130</v>
@@ -11612,10 +11611,10 @@
         <v>90</v>
       </c>
       <c r="H4" s="34" t="s">
+        <v>561</v>
+      </c>
+      <c r="I4" s="34" t="s">
         <v>562</v>
-      </c>
-      <c r="I4" s="34" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -11623,7 +11622,7 @@
         <v>273</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C5" t="s">
         <v>234</v>
@@ -11651,7 +11650,7 @@
         <v>273</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C6" t="s">
         <v>234</v>
@@ -11707,7 +11706,7 @@
         <v>273</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C8" t="s">
         <v>234</v>
@@ -11735,7 +11734,7 @@
         <v>273</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C9" t="s">
         <v>234</v>
@@ -11763,7 +11762,7 @@
         <v>273</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C10" t="s">
         <v>234</v>
@@ -11845,7 +11844,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="108" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B1" s="108"/>
       <c r="C1" s="108"/>
@@ -11864,25 +11863,25 @@
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>394</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>395</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>396</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>397</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>398</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -11894,13 +11893,13 @@
     </row>
     <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
+        <v>400</v>
+      </c>
+      <c r="B5" s="54" t="s">
         <v>401</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="C5" s="55" t="s">
         <v>402</v>
-      </c>
-      <c r="C5" s="55" t="s">
-        <v>403</v>
       </c>
       <c r="D5" s="55">
         <v>56</v>
@@ -11915,13 +11914,13 @@
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
+        <v>403</v>
+      </c>
+      <c r="B6" s="57" t="s">
         <v>404</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="C6" s="55" t="s">
         <v>405</v>
-      </c>
-      <c r="C6" s="55" t="s">
-        <v>406</v>
       </c>
       <c r="D6" s="55">
         <v>56</v>
@@ -11937,13 +11936,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
+        <v>406</v>
+      </c>
+      <c r="B7" s="57" t="s">
         <v>407</v>
       </c>
-      <c r="B7" s="57" t="s">
-        <v>408</v>
-      </c>
       <c r="C7" s="55" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D7" s="55">
         <v>6</v>
@@ -11958,13 +11957,13 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
+        <v>408</v>
+      </c>
+      <c r="B8" s="57" t="s">
         <v>409</v>
       </c>
-      <c r="B8" s="57" t="s">
-        <v>410</v>
-      </c>
       <c r="C8" s="55" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D8" s="55">
         <v>6</v>
@@ -11979,13 +11978,13 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
+        <v>410</v>
+      </c>
+      <c r="B9" s="57" t="s">
         <v>411</v>
       </c>
-      <c r="B9" s="57" t="s">
-        <v>412</v>
-      </c>
       <c r="C9" s="55" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D9" s="55">
         <v>6</v>
@@ -12000,13 +11999,13 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
+        <v>412</v>
+      </c>
+      <c r="B10" s="57" t="s">
         <v>413</v>
       </c>
-      <c r="B10" s="57" t="s">
-        <v>414</v>
-      </c>
       <c r="C10" s="55" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D10" s="55">
         <v>48</v>
@@ -12022,7 +12021,7 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51"/>
       <c r="B11" s="59" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C11" s="49"/>
       <c r="D11" s="55"/>
@@ -12035,7 +12034,7 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51"/>
       <c r="B12" s="60" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C12" s="61"/>
       <c r="D12" s="61"/>

--- a/TAZA/_документы/Бюджет ТАЗА – 2 месяца (ноябрь–декабрь).xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА – 2 месяца (ноябрь–декабрь).xlsx
@@ -2108,9 +2108,6 @@
     <t>Финансирование</t>
   </si>
   <si>
-    <t>Разница с 250 млн (+ остаток / − не хватает)</t>
-  </si>
-  <si>
     <t>Бюджет ЦАКФ на ноябрь–декабрь 2026 года, ₸</t>
   </si>
   <si>
@@ -2124,6 +2121,9 @@
   </si>
   <si>
     <t>ВСЕГО (А + Б)</t>
+  </si>
+  <si>
+    <t>Разница с 250 млн (+ остаток / − дефицит)</t>
   </si>
 </sst>
 </file>
@@ -2846,7 +2846,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -2860,7 +2860,7 @@
         <v>562</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2893,7 +2893,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B6" s="38">
         <f>(SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36*(Штат!$I$5:$I$36&lt;=2)))+B7+B20</f>
@@ -3129,7 +3129,7 @@
     </row>
     <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="39" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B20" s="40">
         <v>37450000</v>
@@ -3144,7 +3144,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="43" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B21" s="44">
         <f>B18+B19</f>
@@ -3185,7 +3185,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="43" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="B25" s="44">
         <f>$D$24-B23</f>
